--- a/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -2611,92 +2611,92 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="3">
@@ -2835,92 +2835,92 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="5">
@@ -2949,6 +2949,90 @@
         <is>
           <t>EMPTY</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
+        <v/>
+      </c>
+      <c r="R5" t="n">
+        <v/>
+      </c>
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
+        <v/>
+      </c>
+      <c r="AA5" t="n">
+        <v/>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
+      </c>
+      <c r="AJ5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2975,92 +3059,92 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="7">
@@ -3087,7 +3171,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -3199,92 +3283,92 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ8" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="9">
@@ -3314,6 +3398,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
+        <v/>
+      </c>
+      <c r="R9" t="n">
+        <v/>
+      </c>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
+        <v/>
+      </c>
+      <c r="AA9" t="n">
+        <v/>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
+      </c>
+      <c r="AJ9" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3339,92 +3507,92 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ10" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="11">
@@ -3563,92 +3731,92 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ12" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="13">
@@ -3678,6 +3846,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v/>
+      </c>
+      <c r="K13" t="n">
+        <v/>
+      </c>
+      <c r="L13" t="n">
+        <v/>
+      </c>
+      <c r="M13" t="n">
+        <v/>
+      </c>
+      <c r="N13" t="n">
+        <v/>
+      </c>
+      <c r="O13" t="n">
+        <v/>
+      </c>
+      <c r="P13" t="n">
+        <v/>
+      </c>
+      <c r="Q13" t="n">
+        <v/>
+      </c>
+      <c r="R13" t="n">
+        <v/>
+      </c>
+      <c r="S13" t="n">
+        <v/>
+      </c>
+      <c r="T13" t="n">
+        <v/>
+      </c>
+      <c r="U13" t="n">
+        <v/>
+      </c>
+      <c r="V13" t="n">
+        <v/>
+      </c>
+      <c r="W13" t="n">
+        <v/>
+      </c>
+      <c r="X13" t="n">
+        <v/>
+      </c>
+      <c r="Y13" t="n">
+        <v/>
+      </c>
+      <c r="Z13" t="n">
+        <v/>
+      </c>
+      <c r="AA13" t="n">
+        <v/>
+      </c>
+      <c r="AB13" t="n">
+        <v/>
+      </c>
+      <c r="AC13" t="n">
+        <v/>
+      </c>
+      <c r="AD13" t="n">
+        <v/>
+      </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
+      <c r="AI13" t="n">
+        <v/>
+      </c>
+      <c r="AJ13" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3703,92 +3955,92 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="15">
@@ -3818,6 +4070,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v/>
+      </c>
+      <c r="K15" t="n">
+        <v/>
+      </c>
+      <c r="L15" t="n">
+        <v/>
+      </c>
+      <c r="M15" t="n">
+        <v/>
+      </c>
+      <c r="N15" t="n">
+        <v/>
+      </c>
+      <c r="O15" t="n">
+        <v/>
+      </c>
+      <c r="P15" t="n">
+        <v/>
+      </c>
+      <c r="Q15" t="n">
+        <v/>
+      </c>
+      <c r="R15" t="n">
+        <v/>
+      </c>
+      <c r="S15" t="n">
+        <v/>
+      </c>
+      <c r="T15" t="n">
+        <v/>
+      </c>
+      <c r="U15" t="n">
+        <v/>
+      </c>
+      <c r="V15" t="n">
+        <v/>
+      </c>
+      <c r="W15" t="n">
+        <v/>
+      </c>
+      <c r="X15" t="n">
+        <v/>
+      </c>
+      <c r="Y15" t="n">
+        <v/>
+      </c>
+      <c r="Z15" t="n">
+        <v/>
+      </c>
+      <c r="AA15" t="n">
+        <v/>
+      </c>
+      <c r="AB15" t="n">
+        <v/>
+      </c>
+      <c r="AC15" t="n">
+        <v/>
+      </c>
+      <c r="AD15" t="n">
+        <v/>
+      </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="n">
+        <v/>
+      </c>
+      <c r="AI15" t="n">
+        <v/>
+      </c>
+      <c r="AJ15" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3843,92 +4179,92 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ16" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="17">
@@ -3958,6 +4294,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v/>
+      </c>
+      <c r="K17" t="n">
+        <v/>
+      </c>
+      <c r="L17" t="n">
+        <v/>
+      </c>
+      <c r="M17" t="n">
+        <v/>
+      </c>
+      <c r="N17" t="n">
+        <v/>
+      </c>
+      <c r="O17" t="n">
+        <v/>
+      </c>
+      <c r="P17" t="n">
+        <v/>
+      </c>
+      <c r="Q17" t="n">
+        <v/>
+      </c>
+      <c r="R17" t="n">
+        <v/>
+      </c>
+      <c r="S17" t="n">
+        <v/>
+      </c>
+      <c r="T17" t="n">
+        <v/>
+      </c>
+      <c r="U17" t="n">
+        <v/>
+      </c>
+      <c r="V17" t="n">
+        <v/>
+      </c>
+      <c r="W17" t="n">
+        <v/>
+      </c>
+      <c r="X17" t="n">
+        <v/>
+      </c>
+      <c r="Y17" t="n">
+        <v/>
+      </c>
+      <c r="Z17" t="n">
+        <v/>
+      </c>
+      <c r="AA17" t="n">
+        <v/>
+      </c>
+      <c r="AB17" t="n">
+        <v/>
+      </c>
+      <c r="AC17" t="n">
+        <v/>
+      </c>
+      <c r="AD17" t="n">
+        <v/>
+      </c>
+      <c r="AE17" t="n">
+        <v/>
+      </c>
+      <c r="AF17" t="n">
+        <v/>
+      </c>
+      <c r="AG17" t="n">
+        <v/>
+      </c>
+      <c r="AH17" t="n">
+        <v/>
+      </c>
+      <c r="AI17" t="n">
+        <v/>
+      </c>
+      <c r="AJ17" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3983,92 +4403,92 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="19">
@@ -4098,6 +4518,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v/>
+      </c>
+      <c r="K19" t="n">
+        <v/>
+      </c>
+      <c r="L19" t="n">
+        <v/>
+      </c>
+      <c r="M19" t="n">
+        <v/>
+      </c>
+      <c r="N19" t="n">
+        <v/>
+      </c>
+      <c r="O19" t="n">
+        <v/>
+      </c>
+      <c r="P19" t="n">
+        <v/>
+      </c>
+      <c r="Q19" t="n">
+        <v/>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="n">
+        <v/>
+      </c>
+      <c r="T19" t="n">
+        <v/>
+      </c>
+      <c r="U19" t="n">
+        <v/>
+      </c>
+      <c r="V19" t="n">
+        <v/>
+      </c>
+      <c r="W19" t="n">
+        <v/>
+      </c>
+      <c r="X19" t="n">
+        <v/>
+      </c>
+      <c r="Y19" t="n">
+        <v/>
+      </c>
+      <c r="Z19" t="n">
+        <v/>
+      </c>
+      <c r="AA19" t="n">
+        <v/>
+      </c>
+      <c r="AB19" t="n">
+        <v/>
+      </c>
+      <c r="AC19" t="n">
+        <v/>
+      </c>
+      <c r="AD19" t="n">
+        <v/>
+      </c>
+      <c r="AE19" t="n">
+        <v/>
+      </c>
+      <c r="AF19" t="n">
+        <v/>
+      </c>
+      <c r="AG19" t="n">
+        <v/>
+      </c>
+      <c r="AH19" t="n">
+        <v/>
+      </c>
+      <c r="AI19" t="n">
+        <v/>
+      </c>
+      <c r="AJ19" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4123,92 +4627,92 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="21">
@@ -4238,6 +4742,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v/>
+      </c>
+      <c r="K21" t="n">
+        <v/>
+      </c>
+      <c r="L21" t="n">
+        <v/>
+      </c>
+      <c r="M21" t="n">
+        <v/>
+      </c>
+      <c r="N21" t="n">
+        <v/>
+      </c>
+      <c r="O21" t="n">
+        <v/>
+      </c>
+      <c r="P21" t="n">
+        <v/>
+      </c>
+      <c r="Q21" t="n">
+        <v/>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="n">
+        <v/>
+      </c>
+      <c r="T21" t="n">
+        <v/>
+      </c>
+      <c r="U21" t="n">
+        <v/>
+      </c>
+      <c r="V21" t="n">
+        <v/>
+      </c>
+      <c r="W21" t="n">
+        <v/>
+      </c>
+      <c r="X21" t="n">
+        <v/>
+      </c>
+      <c r="Y21" t="n">
+        <v/>
+      </c>
+      <c r="Z21" t="n">
+        <v/>
+      </c>
+      <c r="AA21" t="n">
+        <v/>
+      </c>
+      <c r="AB21" t="n">
+        <v/>
+      </c>
+      <c r="AC21" t="n">
+        <v/>
+      </c>
+      <c r="AD21" t="n">
+        <v/>
+      </c>
+      <c r="AE21" t="n">
+        <v/>
+      </c>
+      <c r="AF21" t="n">
+        <v/>
+      </c>
+      <c r="AG21" t="n">
+        <v/>
+      </c>
+      <c r="AH21" t="n">
+        <v/>
+      </c>
+      <c r="AI21" t="n">
+        <v/>
+      </c>
+      <c r="AJ21" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4263,92 +4851,92 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="23">
@@ -4378,6 +4966,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I23" t="n">
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v/>
+      </c>
+      <c r="K23" t="n">
+        <v/>
+      </c>
+      <c r="L23" t="n">
+        <v/>
+      </c>
+      <c r="M23" t="n">
+        <v/>
+      </c>
+      <c r="N23" t="n">
+        <v/>
+      </c>
+      <c r="O23" t="n">
+        <v/>
+      </c>
+      <c r="P23" t="n">
+        <v/>
+      </c>
+      <c r="Q23" t="n">
+        <v/>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="n">
+        <v/>
+      </c>
+      <c r="T23" t="n">
+        <v/>
+      </c>
+      <c r="U23" t="n">
+        <v/>
+      </c>
+      <c r="V23" t="n">
+        <v/>
+      </c>
+      <c r="W23" t="n">
+        <v/>
+      </c>
+      <c r="X23" t="n">
+        <v/>
+      </c>
+      <c r="Y23" t="n">
+        <v/>
+      </c>
+      <c r="Z23" t="n">
+        <v/>
+      </c>
+      <c r="AA23" t="n">
+        <v/>
+      </c>
+      <c r="AB23" t="n">
+        <v/>
+      </c>
+      <c r="AC23" t="n">
+        <v/>
+      </c>
+      <c r="AD23" t="n">
+        <v/>
+      </c>
+      <c r="AE23" t="n">
+        <v/>
+      </c>
+      <c r="AF23" t="n">
+        <v/>
+      </c>
+      <c r="AG23" t="n">
+        <v/>
+      </c>
+      <c r="AH23" t="n">
+        <v/>
+      </c>
+      <c r="AI23" t="n">
+        <v/>
+      </c>
+      <c r="AJ23" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4403,92 +5075,92 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ24" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="25">
@@ -4518,6 +5190,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I25" t="n">
+        <v/>
+      </c>
+      <c r="J25" t="n">
+        <v/>
+      </c>
+      <c r="K25" t="n">
+        <v/>
+      </c>
+      <c r="L25" t="n">
+        <v/>
+      </c>
+      <c r="M25" t="n">
+        <v/>
+      </c>
+      <c r="N25" t="n">
+        <v/>
+      </c>
+      <c r="O25" t="n">
+        <v/>
+      </c>
+      <c r="P25" t="n">
+        <v/>
+      </c>
+      <c r="Q25" t="n">
+        <v/>
+      </c>
+      <c r="R25" t="n">
+        <v/>
+      </c>
+      <c r="S25" t="n">
+        <v/>
+      </c>
+      <c r="T25" t="n">
+        <v/>
+      </c>
+      <c r="U25" t="n">
+        <v/>
+      </c>
+      <c r="V25" t="n">
+        <v/>
+      </c>
+      <c r="W25" t="n">
+        <v/>
+      </c>
+      <c r="X25" t="n">
+        <v/>
+      </c>
+      <c r="Y25" t="n">
+        <v/>
+      </c>
+      <c r="Z25" t="n">
+        <v/>
+      </c>
+      <c r="AA25" t="n">
+        <v/>
+      </c>
+      <c r="AB25" t="n">
+        <v/>
+      </c>
+      <c r="AC25" t="n">
+        <v/>
+      </c>
+      <c r="AD25" t="n">
+        <v/>
+      </c>
+      <c r="AE25" t="n">
+        <v/>
+      </c>
+      <c r="AF25" t="n">
+        <v/>
+      </c>
+      <c r="AG25" t="n">
+        <v/>
+      </c>
+      <c r="AH25" t="n">
+        <v/>
+      </c>
+      <c r="AI25" t="n">
+        <v/>
+      </c>
+      <c r="AJ25" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4543,92 +5299,92 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ26" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="27">
@@ -4658,6 +5414,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I27" t="n">
+        <v/>
+      </c>
+      <c r="J27" t="n">
+        <v/>
+      </c>
+      <c r="K27" t="n">
+        <v/>
+      </c>
+      <c r="L27" t="n">
+        <v/>
+      </c>
+      <c r="M27" t="n">
+        <v/>
+      </c>
+      <c r="N27" t="n">
+        <v/>
+      </c>
+      <c r="O27" t="n">
+        <v/>
+      </c>
+      <c r="P27" t="n">
+        <v/>
+      </c>
+      <c r="Q27" t="n">
+        <v/>
+      </c>
+      <c r="R27" t="n">
+        <v/>
+      </c>
+      <c r="S27" t="n">
+        <v/>
+      </c>
+      <c r="T27" t="n">
+        <v/>
+      </c>
+      <c r="U27" t="n">
+        <v/>
+      </c>
+      <c r="V27" t="n">
+        <v/>
+      </c>
+      <c r="W27" t="n">
+        <v/>
+      </c>
+      <c r="X27" t="n">
+        <v/>
+      </c>
+      <c r="Y27" t="n">
+        <v/>
+      </c>
+      <c r="Z27" t="n">
+        <v/>
+      </c>
+      <c r="AA27" t="n">
+        <v/>
+      </c>
+      <c r="AB27" t="n">
+        <v/>
+      </c>
+      <c r="AC27" t="n">
+        <v/>
+      </c>
+      <c r="AD27" t="n">
+        <v/>
+      </c>
+      <c r="AE27" t="n">
+        <v/>
+      </c>
+      <c r="AF27" t="n">
+        <v/>
+      </c>
+      <c r="AG27" t="n">
+        <v/>
+      </c>
+      <c r="AH27" t="n">
+        <v/>
+      </c>
+      <c r="AI27" t="n">
+        <v/>
+      </c>
+      <c r="AJ27" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4683,92 +5523,92 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ28" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="29">
@@ -4798,6 +5638,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I29" t="n">
+        <v/>
+      </c>
+      <c r="J29" t="n">
+        <v/>
+      </c>
+      <c r="K29" t="n">
+        <v/>
+      </c>
+      <c r="L29" t="n">
+        <v/>
+      </c>
+      <c r="M29" t="n">
+        <v/>
+      </c>
+      <c r="N29" t="n">
+        <v/>
+      </c>
+      <c r="O29" t="n">
+        <v/>
+      </c>
+      <c r="P29" t="n">
+        <v/>
+      </c>
+      <c r="Q29" t="n">
+        <v/>
+      </c>
+      <c r="R29" t="n">
+        <v/>
+      </c>
+      <c r="S29" t="n">
+        <v/>
+      </c>
+      <c r="T29" t="n">
+        <v/>
+      </c>
+      <c r="U29" t="n">
+        <v/>
+      </c>
+      <c r="V29" t="n">
+        <v/>
+      </c>
+      <c r="W29" t="n">
+        <v/>
+      </c>
+      <c r="X29" t="n">
+        <v/>
+      </c>
+      <c r="Y29" t="n">
+        <v/>
+      </c>
+      <c r="Z29" t="n">
+        <v/>
+      </c>
+      <c r="AA29" t="n">
+        <v/>
+      </c>
+      <c r="AB29" t="n">
+        <v/>
+      </c>
+      <c r="AC29" t="n">
+        <v/>
+      </c>
+      <c r="AD29" t="n">
+        <v/>
+      </c>
+      <c r="AE29" t="n">
+        <v/>
+      </c>
+      <c r="AF29" t="n">
+        <v/>
+      </c>
+      <c r="AG29" t="n">
+        <v/>
+      </c>
+      <c r="AH29" t="n">
+        <v/>
+      </c>
+      <c r="AI29" t="n">
+        <v/>
+      </c>
+      <c r="AJ29" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4823,92 +5747,92 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ30" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="31">
@@ -4938,6 +5862,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I31" t="n">
+        <v/>
+      </c>
+      <c r="J31" t="n">
+        <v/>
+      </c>
+      <c r="K31" t="n">
+        <v/>
+      </c>
+      <c r="L31" t="n">
+        <v/>
+      </c>
+      <c r="M31" t="n">
+        <v/>
+      </c>
+      <c r="N31" t="n">
+        <v/>
+      </c>
+      <c r="O31" t="n">
+        <v/>
+      </c>
+      <c r="P31" t="n">
+        <v/>
+      </c>
+      <c r="Q31" t="n">
+        <v/>
+      </c>
+      <c r="R31" t="n">
+        <v/>
+      </c>
+      <c r="S31" t="n">
+        <v/>
+      </c>
+      <c r="T31" t="n">
+        <v/>
+      </c>
+      <c r="U31" t="n">
+        <v/>
+      </c>
+      <c r="V31" t="n">
+        <v/>
+      </c>
+      <c r="W31" t="n">
+        <v/>
+      </c>
+      <c r="X31" t="n">
+        <v/>
+      </c>
+      <c r="Y31" t="n">
+        <v/>
+      </c>
+      <c r="Z31" t="n">
+        <v/>
+      </c>
+      <c r="AA31" t="n">
+        <v/>
+      </c>
+      <c r="AB31" t="n">
+        <v/>
+      </c>
+      <c r="AC31" t="n">
+        <v/>
+      </c>
+      <c r="AD31" t="n">
+        <v/>
+      </c>
+      <c r="AE31" t="n">
+        <v/>
+      </c>
+      <c r="AF31" t="n">
+        <v/>
+      </c>
+      <c r="AG31" t="n">
+        <v/>
+      </c>
+      <c r="AH31" t="n">
+        <v/>
+      </c>
+      <c r="AI31" t="n">
+        <v/>
+      </c>
+      <c r="AJ31" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4963,92 +5971,92 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ32" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="33">
@@ -5078,6 +6086,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I33" t="n">
+        <v/>
+      </c>
+      <c r="J33" t="n">
+        <v/>
+      </c>
+      <c r="K33" t="n">
+        <v/>
+      </c>
+      <c r="L33" t="n">
+        <v/>
+      </c>
+      <c r="M33" t="n">
+        <v/>
+      </c>
+      <c r="N33" t="n">
+        <v/>
+      </c>
+      <c r="O33" t="n">
+        <v/>
+      </c>
+      <c r="P33" t="n">
+        <v/>
+      </c>
+      <c r="Q33" t="n">
+        <v/>
+      </c>
+      <c r="R33" t="n">
+        <v/>
+      </c>
+      <c r="S33" t="n">
+        <v/>
+      </c>
+      <c r="T33" t="n">
+        <v/>
+      </c>
+      <c r="U33" t="n">
+        <v/>
+      </c>
+      <c r="V33" t="n">
+        <v/>
+      </c>
+      <c r="W33" t="n">
+        <v/>
+      </c>
+      <c r="X33" t="n">
+        <v/>
+      </c>
+      <c r="Y33" t="n">
+        <v/>
+      </c>
+      <c r="Z33" t="n">
+        <v/>
+      </c>
+      <c r="AA33" t="n">
+        <v/>
+      </c>
+      <c r="AB33" t="n">
+        <v/>
+      </c>
+      <c r="AC33" t="n">
+        <v/>
+      </c>
+      <c r="AD33" t="n">
+        <v/>
+      </c>
+      <c r="AE33" t="n">
+        <v/>
+      </c>
+      <c r="AF33" t="n">
+        <v/>
+      </c>
+      <c r="AG33" t="n">
+        <v/>
+      </c>
+      <c r="AH33" t="n">
+        <v/>
+      </c>
+      <c r="AI33" t="n">
+        <v/>
+      </c>
+      <c r="AJ33" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5103,92 +6195,92 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ34" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="35">
@@ -5218,6 +6310,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I35" t="n">
+        <v/>
+      </c>
+      <c r="J35" t="n">
+        <v/>
+      </c>
+      <c r="K35" t="n">
+        <v/>
+      </c>
+      <c r="L35" t="n">
+        <v/>
+      </c>
+      <c r="M35" t="n">
+        <v/>
+      </c>
+      <c r="N35" t="n">
+        <v/>
+      </c>
+      <c r="O35" t="n">
+        <v/>
+      </c>
+      <c r="P35" t="n">
+        <v/>
+      </c>
+      <c r="Q35" t="n">
+        <v/>
+      </c>
+      <c r="R35" t="n">
+        <v/>
+      </c>
+      <c r="S35" t="n">
+        <v/>
+      </c>
+      <c r="T35" t="n">
+        <v/>
+      </c>
+      <c r="U35" t="n">
+        <v/>
+      </c>
+      <c r="V35" t="n">
+        <v/>
+      </c>
+      <c r="W35" t="n">
+        <v/>
+      </c>
+      <c r="X35" t="n">
+        <v/>
+      </c>
+      <c r="Y35" t="n">
+        <v/>
+      </c>
+      <c r="Z35" t="n">
+        <v/>
+      </c>
+      <c r="AA35" t="n">
+        <v/>
+      </c>
+      <c r="AB35" t="n">
+        <v/>
+      </c>
+      <c r="AC35" t="n">
+        <v/>
+      </c>
+      <c r="AD35" t="n">
+        <v/>
+      </c>
+      <c r="AE35" t="n">
+        <v/>
+      </c>
+      <c r="AF35" t="n">
+        <v/>
+      </c>
+      <c r="AG35" t="n">
+        <v/>
+      </c>
+      <c r="AH35" t="n">
+        <v/>
+      </c>
+      <c r="AI35" t="n">
+        <v/>
+      </c>
+      <c r="AJ35" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5243,92 +6419,92 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ36" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="37">
@@ -5358,6 +6534,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I37" t="n">
+        <v/>
+      </c>
+      <c r="J37" t="n">
+        <v/>
+      </c>
+      <c r="K37" t="n">
+        <v/>
+      </c>
+      <c r="L37" t="n">
+        <v/>
+      </c>
+      <c r="M37" t="n">
+        <v/>
+      </c>
+      <c r="N37" t="n">
+        <v/>
+      </c>
+      <c r="O37" t="n">
+        <v/>
+      </c>
+      <c r="P37" t="n">
+        <v/>
+      </c>
+      <c r="Q37" t="n">
+        <v/>
+      </c>
+      <c r="R37" t="n">
+        <v/>
+      </c>
+      <c r="S37" t="n">
+        <v/>
+      </c>
+      <c r="T37" t="n">
+        <v/>
+      </c>
+      <c r="U37" t="n">
+        <v/>
+      </c>
+      <c r="V37" t="n">
+        <v/>
+      </c>
+      <c r="W37" t="n">
+        <v/>
+      </c>
+      <c r="X37" t="n">
+        <v/>
+      </c>
+      <c r="Y37" t="n">
+        <v/>
+      </c>
+      <c r="Z37" t="n">
+        <v/>
+      </c>
+      <c r="AA37" t="n">
+        <v/>
+      </c>
+      <c r="AB37" t="n">
+        <v/>
+      </c>
+      <c r="AC37" t="n">
+        <v/>
+      </c>
+      <c r="AD37" t="n">
+        <v/>
+      </c>
+      <c r="AE37" t="n">
+        <v/>
+      </c>
+      <c r="AF37" t="n">
+        <v/>
+      </c>
+      <c r="AG37" t="n">
+        <v/>
+      </c>
+      <c r="AH37" t="n">
+        <v/>
+      </c>
+      <c r="AI37" t="n">
+        <v/>
+      </c>
+      <c r="AJ37" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5383,92 +6643,92 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ38" t="n">
-        <v>20833.33</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="39">
@@ -5498,6 +6758,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I39" t="n">
+        <v/>
+      </c>
+      <c r="J39" t="n">
+        <v/>
+      </c>
+      <c r="K39" t="n">
+        <v/>
+      </c>
+      <c r="L39" t="n">
+        <v/>
+      </c>
+      <c r="M39" t="n">
+        <v/>
+      </c>
+      <c r="N39" t="n">
+        <v/>
+      </c>
+      <c r="O39" t="n">
+        <v/>
+      </c>
+      <c r="P39" t="n">
+        <v/>
+      </c>
+      <c r="Q39" t="n">
+        <v/>
+      </c>
+      <c r="R39" t="n">
+        <v/>
+      </c>
+      <c r="S39" t="n">
+        <v/>
+      </c>
+      <c r="T39" t="n">
+        <v/>
+      </c>
+      <c r="U39" t="n">
+        <v/>
+      </c>
+      <c r="V39" t="n">
+        <v/>
+      </c>
+      <c r="W39" t="n">
+        <v/>
+      </c>
+      <c r="X39" t="n">
+        <v/>
+      </c>
+      <c r="Y39" t="n">
+        <v/>
+      </c>
+      <c r="Z39" t="n">
+        <v/>
+      </c>
+      <c r="AA39" t="n">
+        <v/>
+      </c>
+      <c r="AB39" t="n">
+        <v/>
+      </c>
+      <c r="AC39" t="n">
+        <v/>
+      </c>
+      <c r="AD39" t="n">
+        <v/>
+      </c>
+      <c r="AE39" t="n">
+        <v/>
+      </c>
+      <c r="AF39" t="n">
+        <v/>
+      </c>
+      <c r="AG39" t="n">
+        <v/>
+      </c>
+      <c r="AH39" t="n">
+        <v/>
+      </c>
+      <c r="AI39" t="n">
+        <v/>
+      </c>
+      <c r="AJ39" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5523,92 +6867,92 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ40" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="41">
@@ -5638,6 +6982,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I41" t="n">
+        <v/>
+      </c>
+      <c r="J41" t="n">
+        <v/>
+      </c>
+      <c r="K41" t="n">
+        <v/>
+      </c>
+      <c r="L41" t="n">
+        <v/>
+      </c>
+      <c r="M41" t="n">
+        <v/>
+      </c>
+      <c r="N41" t="n">
+        <v/>
+      </c>
+      <c r="O41" t="n">
+        <v/>
+      </c>
+      <c r="P41" t="n">
+        <v/>
+      </c>
+      <c r="Q41" t="n">
+        <v/>
+      </c>
+      <c r="R41" t="n">
+        <v/>
+      </c>
+      <c r="S41" t="n">
+        <v/>
+      </c>
+      <c r="T41" t="n">
+        <v/>
+      </c>
+      <c r="U41" t="n">
+        <v/>
+      </c>
+      <c r="V41" t="n">
+        <v/>
+      </c>
+      <c r="W41" t="n">
+        <v/>
+      </c>
+      <c r="X41" t="n">
+        <v/>
+      </c>
+      <c r="Y41" t="n">
+        <v/>
+      </c>
+      <c r="Z41" t="n">
+        <v/>
+      </c>
+      <c r="AA41" t="n">
+        <v/>
+      </c>
+      <c r="AB41" t="n">
+        <v/>
+      </c>
+      <c r="AC41" t="n">
+        <v/>
+      </c>
+      <c r="AD41" t="n">
+        <v/>
+      </c>
+      <c r="AE41" t="n">
+        <v/>
+      </c>
+      <c r="AF41" t="n">
+        <v/>
+      </c>
+      <c r="AG41" t="n">
+        <v/>
+      </c>
+      <c r="AH41" t="n">
+        <v/>
+      </c>
+      <c r="AI41" t="n">
+        <v/>
+      </c>
+      <c r="AJ41" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5663,92 +7091,92 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ42" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="43">
@@ -5887,92 +7315,92 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="J44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="K44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="L44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="M44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="N44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="O44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="P44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="Q44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="R44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="S44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="T44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="U44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="V44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="W44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="X44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="Y44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="Z44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="AA44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="AB44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="AC44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="AD44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="AE44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="AF44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="AG44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="AH44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="AI44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
       <c r="AJ44" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316784</v>
       </c>
     </row>
     <row r="45">
@@ -5999,7 +7427,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -6111,92 +7539,92 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ46" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="47">
@@ -6226,6 +7654,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I47" t="n">
+        <v/>
+      </c>
+      <c r="J47" t="n">
+        <v/>
+      </c>
+      <c r="K47" t="n">
+        <v/>
+      </c>
+      <c r="L47" t="n">
+        <v/>
+      </c>
+      <c r="M47" t="n">
+        <v/>
+      </c>
+      <c r="N47" t="n">
+        <v/>
+      </c>
+      <c r="O47" t="n">
+        <v/>
+      </c>
+      <c r="P47" t="n">
+        <v/>
+      </c>
+      <c r="Q47" t="n">
+        <v/>
+      </c>
+      <c r="R47" t="n">
+        <v/>
+      </c>
+      <c r="S47" t="n">
+        <v/>
+      </c>
+      <c r="T47" t="n">
+        <v/>
+      </c>
+      <c r="U47" t="n">
+        <v/>
+      </c>
+      <c r="V47" t="n">
+        <v/>
+      </c>
+      <c r="W47" t="n">
+        <v/>
+      </c>
+      <c r="X47" t="n">
+        <v/>
+      </c>
+      <c r="Y47" t="n">
+        <v/>
+      </c>
+      <c r="Z47" t="n">
+        <v/>
+      </c>
+      <c r="AA47" t="n">
+        <v/>
+      </c>
+      <c r="AB47" t="n">
+        <v/>
+      </c>
+      <c r="AC47" t="n">
+        <v/>
+      </c>
+      <c r="AD47" t="n">
+        <v/>
+      </c>
+      <c r="AE47" t="n">
+        <v/>
+      </c>
+      <c r="AF47" t="n">
+        <v/>
+      </c>
+      <c r="AG47" t="n">
+        <v/>
+      </c>
+      <c r="AH47" t="n">
+        <v/>
+      </c>
+      <c r="AI47" t="n">
+        <v/>
+      </c>
+      <c r="AJ47" t="n">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6251,92 +7763,92 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ48" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="49">
@@ -6475,92 +7987,92 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ50" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="51">
@@ -6590,6 +8102,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I51" t="n">
+        <v/>
+      </c>
+      <c r="J51" t="n">
+        <v/>
+      </c>
+      <c r="K51" t="n">
+        <v/>
+      </c>
+      <c r="L51" t="n">
+        <v/>
+      </c>
+      <c r="M51" t="n">
+        <v/>
+      </c>
+      <c r="N51" t="n">
+        <v/>
+      </c>
+      <c r="O51" t="n">
+        <v/>
+      </c>
+      <c r="P51" t="n">
+        <v/>
+      </c>
+      <c r="Q51" t="n">
+        <v/>
+      </c>
+      <c r="R51" t="n">
+        <v/>
+      </c>
+      <c r="S51" t="n">
+        <v/>
+      </c>
+      <c r="T51" t="n">
+        <v/>
+      </c>
+      <c r="U51" t="n">
+        <v/>
+      </c>
+      <c r="V51" t="n">
+        <v/>
+      </c>
+      <c r="W51" t="n">
+        <v/>
+      </c>
+      <c r="X51" t="n">
+        <v/>
+      </c>
+      <c r="Y51" t="n">
+        <v/>
+      </c>
+      <c r="Z51" t="n">
+        <v/>
+      </c>
+      <c r="AA51" t="n">
+        <v/>
+      </c>
+      <c r="AB51" t="n">
+        <v/>
+      </c>
+      <c r="AC51" t="n">
+        <v/>
+      </c>
+      <c r="AD51" t="n">
+        <v/>
+      </c>
+      <c r="AE51" t="n">
+        <v/>
+      </c>
+      <c r="AF51" t="n">
+        <v/>
+      </c>
+      <c r="AG51" t="n">
+        <v/>
+      </c>
+      <c r="AH51" t="n">
+        <v/>
+      </c>
+      <c r="AI51" t="n">
+        <v/>
+      </c>
+      <c r="AJ51" t="n">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6615,92 +8211,92 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ52" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="53">
@@ -6730,6 +8326,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I53" t="n">
+        <v/>
+      </c>
+      <c r="J53" t="n">
+        <v/>
+      </c>
+      <c r="K53" t="n">
+        <v/>
+      </c>
+      <c r="L53" t="n">
+        <v/>
+      </c>
+      <c r="M53" t="n">
+        <v/>
+      </c>
+      <c r="N53" t="n">
+        <v/>
+      </c>
+      <c r="O53" t="n">
+        <v/>
+      </c>
+      <c r="P53" t="n">
+        <v/>
+      </c>
+      <c r="Q53" t="n">
+        <v/>
+      </c>
+      <c r="R53" t="n">
+        <v/>
+      </c>
+      <c r="S53" t="n">
+        <v/>
+      </c>
+      <c r="T53" t="n">
+        <v/>
+      </c>
+      <c r="U53" t="n">
+        <v/>
+      </c>
+      <c r="V53" t="n">
+        <v/>
+      </c>
+      <c r="W53" t="n">
+        <v/>
+      </c>
+      <c r="X53" t="n">
+        <v/>
+      </c>
+      <c r="Y53" t="n">
+        <v/>
+      </c>
+      <c r="Z53" t="n">
+        <v/>
+      </c>
+      <c r="AA53" t="n">
+        <v/>
+      </c>
+      <c r="AB53" t="n">
+        <v/>
+      </c>
+      <c r="AC53" t="n">
+        <v/>
+      </c>
+      <c r="AD53" t="n">
+        <v/>
+      </c>
+      <c r="AE53" t="n">
+        <v/>
+      </c>
+      <c r="AF53" t="n">
+        <v/>
+      </c>
+      <c r="AG53" t="n">
+        <v/>
+      </c>
+      <c r="AH53" t="n">
+        <v/>
+      </c>
+      <c r="AI53" t="n">
+        <v/>
+      </c>
+      <c r="AJ53" t="n">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6755,92 +8435,92 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ54" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="55">
@@ -6870,6 +8550,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I55" t="n">
+        <v/>
+      </c>
+      <c r="J55" t="n">
+        <v/>
+      </c>
+      <c r="K55" t="n">
+        <v/>
+      </c>
+      <c r="L55" t="n">
+        <v/>
+      </c>
+      <c r="M55" t="n">
+        <v/>
+      </c>
+      <c r="N55" t="n">
+        <v/>
+      </c>
+      <c r="O55" t="n">
+        <v/>
+      </c>
+      <c r="P55" t="n">
+        <v/>
+      </c>
+      <c r="Q55" t="n">
+        <v/>
+      </c>
+      <c r="R55" t="n">
+        <v/>
+      </c>
+      <c r="S55" t="n">
+        <v/>
+      </c>
+      <c r="T55" t="n">
+        <v/>
+      </c>
+      <c r="U55" t="n">
+        <v/>
+      </c>
+      <c r="V55" t="n">
+        <v/>
+      </c>
+      <c r="W55" t="n">
+        <v/>
+      </c>
+      <c r="X55" t="n">
+        <v/>
+      </c>
+      <c r="Y55" t="n">
+        <v/>
+      </c>
+      <c r="Z55" t="n">
+        <v/>
+      </c>
+      <c r="AA55" t="n">
+        <v/>
+      </c>
+      <c r="AB55" t="n">
+        <v/>
+      </c>
+      <c r="AC55" t="n">
+        <v/>
+      </c>
+      <c r="AD55" t="n">
+        <v/>
+      </c>
+      <c r="AE55" t="n">
+        <v/>
+      </c>
+      <c r="AF55" t="n">
+        <v/>
+      </c>
+      <c r="AG55" t="n">
+        <v/>
+      </c>
+      <c r="AH55" t="n">
+        <v/>
+      </c>
+      <c r="AI55" t="n">
+        <v/>
+      </c>
+      <c r="AJ55" t="n">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6895,92 +8659,92 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ56" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="57">
@@ -7010,6 +8774,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I57" t="n">
+        <v/>
+      </c>
+      <c r="J57" t="n">
+        <v/>
+      </c>
+      <c r="K57" t="n">
+        <v/>
+      </c>
+      <c r="L57" t="n">
+        <v/>
+      </c>
+      <c r="M57" t="n">
+        <v/>
+      </c>
+      <c r="N57" t="n">
+        <v/>
+      </c>
+      <c r="O57" t="n">
+        <v/>
+      </c>
+      <c r="P57" t="n">
+        <v/>
+      </c>
+      <c r="Q57" t="n">
+        <v/>
+      </c>
+      <c r="R57" t="n">
+        <v/>
+      </c>
+      <c r="S57" t="n">
+        <v/>
+      </c>
+      <c r="T57" t="n">
+        <v/>
+      </c>
+      <c r="U57" t="n">
+        <v/>
+      </c>
+      <c r="V57" t="n">
+        <v/>
+      </c>
+      <c r="W57" t="n">
+        <v/>
+      </c>
+      <c r="X57" t="n">
+        <v/>
+      </c>
+      <c r="Y57" t="n">
+        <v/>
+      </c>
+      <c r="Z57" t="n">
+        <v/>
+      </c>
+      <c r="AA57" t="n">
+        <v/>
+      </c>
+      <c r="AB57" t="n">
+        <v/>
+      </c>
+      <c r="AC57" t="n">
+        <v/>
+      </c>
+      <c r="AD57" t="n">
+        <v/>
+      </c>
+      <c r="AE57" t="n">
+        <v/>
+      </c>
+      <c r="AF57" t="n">
+        <v/>
+      </c>
+      <c r="AG57" t="n">
+        <v/>
+      </c>
+      <c r="AH57" t="n">
+        <v/>
+      </c>
+      <c r="AI57" t="n">
+        <v/>
+      </c>
+      <c r="AJ57" t="n">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7035,92 +8883,92 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ58" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="59">
@@ -7150,6 +8998,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I59" t="n">
+        <v/>
+      </c>
+      <c r="J59" t="n">
+        <v/>
+      </c>
+      <c r="K59" t="n">
+        <v/>
+      </c>
+      <c r="L59" t="n">
+        <v/>
+      </c>
+      <c r="M59" t="n">
+        <v/>
+      </c>
+      <c r="N59" t="n">
+        <v/>
+      </c>
+      <c r="O59" t="n">
+        <v/>
+      </c>
+      <c r="P59" t="n">
+        <v/>
+      </c>
+      <c r="Q59" t="n">
+        <v/>
+      </c>
+      <c r="R59" t="n">
+        <v/>
+      </c>
+      <c r="S59" t="n">
+        <v/>
+      </c>
+      <c r="T59" t="n">
+        <v/>
+      </c>
+      <c r="U59" t="n">
+        <v/>
+      </c>
+      <c r="V59" t="n">
+        <v/>
+      </c>
+      <c r="W59" t="n">
+        <v/>
+      </c>
+      <c r="X59" t="n">
+        <v/>
+      </c>
+      <c r="Y59" t="n">
+        <v/>
+      </c>
+      <c r="Z59" t="n">
+        <v/>
+      </c>
+      <c r="AA59" t="n">
+        <v/>
+      </c>
+      <c r="AB59" t="n">
+        <v/>
+      </c>
+      <c r="AC59" t="n">
+        <v/>
+      </c>
+      <c r="AD59" t="n">
+        <v/>
+      </c>
+      <c r="AE59" t="n">
+        <v/>
+      </c>
+      <c r="AF59" t="n">
+        <v/>
+      </c>
+      <c r="AG59" t="n">
+        <v/>
+      </c>
+      <c r="AH59" t="n">
+        <v/>
+      </c>
+      <c r="AI59" t="n">
+        <v/>
+      </c>
+      <c r="AJ59" t="n">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7175,92 +9107,92 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ60" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="61">
@@ -7290,6 +9222,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I61" t="n">
+        <v/>
+      </c>
+      <c r="J61" t="n">
+        <v/>
+      </c>
+      <c r="K61" t="n">
+        <v/>
+      </c>
+      <c r="L61" t="n">
+        <v/>
+      </c>
+      <c r="M61" t="n">
+        <v/>
+      </c>
+      <c r="N61" t="n">
+        <v/>
+      </c>
+      <c r="O61" t="n">
+        <v/>
+      </c>
+      <c r="P61" t="n">
+        <v/>
+      </c>
+      <c r="Q61" t="n">
+        <v/>
+      </c>
+      <c r="R61" t="n">
+        <v/>
+      </c>
+      <c r="S61" t="n">
+        <v/>
+      </c>
+      <c r="T61" t="n">
+        <v/>
+      </c>
+      <c r="U61" t="n">
+        <v/>
+      </c>
+      <c r="V61" t="n">
+        <v/>
+      </c>
+      <c r="W61" t="n">
+        <v/>
+      </c>
+      <c r="X61" t="n">
+        <v/>
+      </c>
+      <c r="Y61" t="n">
+        <v/>
+      </c>
+      <c r="Z61" t="n">
+        <v/>
+      </c>
+      <c r="AA61" t="n">
+        <v/>
+      </c>
+      <c r="AB61" t="n">
+        <v/>
+      </c>
+      <c r="AC61" t="n">
+        <v/>
+      </c>
+      <c r="AD61" t="n">
+        <v/>
+      </c>
+      <c r="AE61" t="n">
+        <v/>
+      </c>
+      <c r="AF61" t="n">
+        <v/>
+      </c>
+      <c r="AG61" t="n">
+        <v/>
+      </c>
+      <c r="AH61" t="n">
+        <v/>
+      </c>
+      <c r="AI61" t="n">
+        <v/>
+      </c>
+      <c r="AJ61" t="n">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7315,92 +9331,92 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ62" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="63">
@@ -7539,92 +9555,92 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ64" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="65">
@@ -7763,92 +9779,92 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ66" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="67">
@@ -7878,6 +9894,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I67" t="n">
+        <v/>
+      </c>
+      <c r="J67" t="n">
+        <v/>
+      </c>
+      <c r="K67" t="n">
+        <v/>
+      </c>
+      <c r="L67" t="n">
+        <v/>
+      </c>
+      <c r="M67" t="n">
+        <v/>
+      </c>
+      <c r="N67" t="n">
+        <v/>
+      </c>
+      <c r="O67" t="n">
+        <v/>
+      </c>
+      <c r="P67" t="n">
+        <v/>
+      </c>
+      <c r="Q67" t="n">
+        <v/>
+      </c>
+      <c r="R67" t="n">
+        <v/>
+      </c>
+      <c r="S67" t="n">
+        <v/>
+      </c>
+      <c r="T67" t="n">
+        <v/>
+      </c>
+      <c r="U67" t="n">
+        <v/>
+      </c>
+      <c r="V67" t="n">
+        <v/>
+      </c>
+      <c r="W67" t="n">
+        <v/>
+      </c>
+      <c r="X67" t="n">
+        <v/>
+      </c>
+      <c r="Y67" t="n">
+        <v/>
+      </c>
+      <c r="Z67" t="n">
+        <v/>
+      </c>
+      <c r="AA67" t="n">
+        <v/>
+      </c>
+      <c r="AB67" t="n">
+        <v/>
+      </c>
+      <c r="AC67" t="n">
+        <v/>
+      </c>
+      <c r="AD67" t="n">
+        <v/>
+      </c>
+      <c r="AE67" t="n">
+        <v/>
+      </c>
+      <c r="AF67" t="n">
+        <v/>
+      </c>
+      <c r="AG67" t="n">
+        <v/>
+      </c>
+      <c r="AH67" t="n">
+        <v/>
+      </c>
+      <c r="AI67" t="n">
+        <v/>
+      </c>
+      <c r="AJ67" t="n">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7903,92 +10003,92 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ68" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="69">
@@ -8018,6 +10118,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I69" t="n">
+        <v/>
+      </c>
+      <c r="J69" t="n">
+        <v/>
+      </c>
+      <c r="K69" t="n">
+        <v/>
+      </c>
+      <c r="L69" t="n">
+        <v/>
+      </c>
+      <c r="M69" t="n">
+        <v/>
+      </c>
+      <c r="N69" t="n">
+        <v/>
+      </c>
+      <c r="O69" t="n">
+        <v/>
+      </c>
+      <c r="P69" t="n">
+        <v/>
+      </c>
+      <c r="Q69" t="n">
+        <v/>
+      </c>
+      <c r="R69" t="n">
+        <v/>
+      </c>
+      <c r="S69" t="n">
+        <v/>
+      </c>
+      <c r="T69" t="n">
+        <v/>
+      </c>
+      <c r="U69" t="n">
+        <v/>
+      </c>
+      <c r="V69" t="n">
+        <v/>
+      </c>
+      <c r="W69" t="n">
+        <v/>
+      </c>
+      <c r="X69" t="n">
+        <v/>
+      </c>
+      <c r="Y69" t="n">
+        <v/>
+      </c>
+      <c r="Z69" t="n">
+        <v/>
+      </c>
+      <c r="AA69" t="n">
+        <v/>
+      </c>
+      <c r="AB69" t="n">
+        <v/>
+      </c>
+      <c r="AC69" t="n">
+        <v/>
+      </c>
+      <c r="AD69" t="n">
+        <v/>
+      </c>
+      <c r="AE69" t="n">
+        <v/>
+      </c>
+      <c r="AF69" t="n">
+        <v/>
+      </c>
+      <c r="AG69" t="n">
+        <v/>
+      </c>
+      <c r="AH69" t="n">
+        <v/>
+      </c>
+      <c r="AI69" t="n">
+        <v/>
+      </c>
+      <c r="AJ69" t="n">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8043,92 +10227,92 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ70" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="71">
@@ -8158,6 +10342,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I71" t="n">
+        <v/>
+      </c>
+      <c r="J71" t="n">
+        <v/>
+      </c>
+      <c r="K71" t="n">
+        <v/>
+      </c>
+      <c r="L71" t="n">
+        <v/>
+      </c>
+      <c r="M71" t="n">
+        <v/>
+      </c>
+      <c r="N71" t="n">
+        <v/>
+      </c>
+      <c r="O71" t="n">
+        <v/>
+      </c>
+      <c r="P71" t="n">
+        <v/>
+      </c>
+      <c r="Q71" t="n">
+        <v/>
+      </c>
+      <c r="R71" t="n">
+        <v/>
+      </c>
+      <c r="S71" t="n">
+        <v/>
+      </c>
+      <c r="T71" t="n">
+        <v/>
+      </c>
+      <c r="U71" t="n">
+        <v/>
+      </c>
+      <c r="V71" t="n">
+        <v/>
+      </c>
+      <c r="W71" t="n">
+        <v/>
+      </c>
+      <c r="X71" t="n">
+        <v/>
+      </c>
+      <c r="Y71" t="n">
+        <v/>
+      </c>
+      <c r="Z71" t="n">
+        <v/>
+      </c>
+      <c r="AA71" t="n">
+        <v/>
+      </c>
+      <c r="AB71" t="n">
+        <v/>
+      </c>
+      <c r="AC71" t="n">
+        <v/>
+      </c>
+      <c r="AD71" t="n">
+        <v/>
+      </c>
+      <c r="AE71" t="n">
+        <v/>
+      </c>
+      <c r="AF71" t="n">
+        <v/>
+      </c>
+      <c r="AG71" t="n">
+        <v/>
+      </c>
+      <c r="AH71" t="n">
+        <v/>
+      </c>
+      <c r="AI71" t="n">
+        <v/>
+      </c>
+      <c r="AJ71" t="n">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8183,92 +10451,92 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ72" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="73">
@@ -8298,6 +10566,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I73" t="n">
+        <v/>
+      </c>
+      <c r="J73" t="n">
+        <v/>
+      </c>
+      <c r="K73" t="n">
+        <v/>
+      </c>
+      <c r="L73" t="n">
+        <v/>
+      </c>
+      <c r="M73" t="n">
+        <v/>
+      </c>
+      <c r="N73" t="n">
+        <v/>
+      </c>
+      <c r="O73" t="n">
+        <v/>
+      </c>
+      <c r="P73" t="n">
+        <v/>
+      </c>
+      <c r="Q73" t="n">
+        <v/>
+      </c>
+      <c r="R73" t="n">
+        <v/>
+      </c>
+      <c r="S73" t="n">
+        <v/>
+      </c>
+      <c r="T73" t="n">
+        <v/>
+      </c>
+      <c r="U73" t="n">
+        <v/>
+      </c>
+      <c r="V73" t="n">
+        <v/>
+      </c>
+      <c r="W73" t="n">
+        <v/>
+      </c>
+      <c r="X73" t="n">
+        <v/>
+      </c>
+      <c r="Y73" t="n">
+        <v/>
+      </c>
+      <c r="Z73" t="n">
+        <v/>
+      </c>
+      <c r="AA73" t="n">
+        <v/>
+      </c>
+      <c r="AB73" t="n">
+        <v/>
+      </c>
+      <c r="AC73" t="n">
+        <v/>
+      </c>
+      <c r="AD73" t="n">
+        <v/>
+      </c>
+      <c r="AE73" t="n">
+        <v/>
+      </c>
+      <c r="AF73" t="n">
+        <v/>
+      </c>
+      <c r="AG73" t="n">
+        <v/>
+      </c>
+      <c r="AH73" t="n">
+        <v/>
+      </c>
+      <c r="AI73" t="n">
+        <v/>
+      </c>
+      <c r="AJ73" t="n">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8323,92 +10675,92 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ74" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="75">
@@ -8438,6 +10790,90 @@
           <t>EMPTY</t>
         </is>
       </c>
+      <c r="I75" t="n">
+        <v/>
+      </c>
+      <c r="J75" t="n">
+        <v/>
+      </c>
+      <c r="K75" t="n">
+        <v/>
+      </c>
+      <c r="L75" t="n">
+        <v/>
+      </c>
+      <c r="M75" t="n">
+        <v/>
+      </c>
+      <c r="N75" t="n">
+        <v/>
+      </c>
+      <c r="O75" t="n">
+        <v/>
+      </c>
+      <c r="P75" t="n">
+        <v/>
+      </c>
+      <c r="Q75" t="n">
+        <v/>
+      </c>
+      <c r="R75" t="n">
+        <v/>
+      </c>
+      <c r="S75" t="n">
+        <v/>
+      </c>
+      <c r="T75" t="n">
+        <v/>
+      </c>
+      <c r="U75" t="n">
+        <v/>
+      </c>
+      <c r="V75" t="n">
+        <v/>
+      </c>
+      <c r="W75" t="n">
+        <v/>
+      </c>
+      <c r="X75" t="n">
+        <v/>
+      </c>
+      <c r="Y75" t="n">
+        <v/>
+      </c>
+      <c r="Z75" t="n">
+        <v/>
+      </c>
+      <c r="AA75" t="n">
+        <v/>
+      </c>
+      <c r="AB75" t="n">
+        <v/>
+      </c>
+      <c r="AC75" t="n">
+        <v/>
+      </c>
+      <c r="AD75" t="n">
+        <v/>
+      </c>
+      <c r="AE75" t="n">
+        <v/>
+      </c>
+      <c r="AF75" t="n">
+        <v/>
+      </c>
+      <c r="AG75" t="n">
+        <v/>
+      </c>
+      <c r="AH75" t="n">
+        <v/>
+      </c>
+      <c r="AI75" t="n">
+        <v/>
+      </c>
+      <c r="AJ75" t="n">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8463,92 +10899,92 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="J76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="K76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="L76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="M76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="N76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="O76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="P76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Q76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="R76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="S76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="T76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="U76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="V76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="W76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="X76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Y76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="Z76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AA76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AB76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AC76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AD76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AE76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AF76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AG76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AH76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AI76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
       <c r="AJ76" t="n">
-        <v>32777.77</v>
+        <v>42050.82742316785</v>
       </c>
     </row>
     <row r="77">
@@ -8577,6 +11013,90 @@
         <is>
           <t>EMPTY</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v/>
+      </c>
+      <c r="J77" t="n">
+        <v/>
+      </c>
+      <c r="K77" t="n">
+        <v/>
+      </c>
+      <c r="L77" t="n">
+        <v/>
+      </c>
+      <c r="M77" t="n">
+        <v/>
+      </c>
+      <c r="N77" t="n">
+        <v/>
+      </c>
+      <c r="O77" t="n">
+        <v/>
+      </c>
+      <c r="P77" t="n">
+        <v/>
+      </c>
+      <c r="Q77" t="n">
+        <v/>
+      </c>
+      <c r="R77" t="n">
+        <v/>
+      </c>
+      <c r="S77" t="n">
+        <v/>
+      </c>
+      <c r="T77" t="n">
+        <v/>
+      </c>
+      <c r="U77" t="n">
+        <v/>
+      </c>
+      <c r="V77" t="n">
+        <v/>
+      </c>
+      <c r="W77" t="n">
+        <v/>
+      </c>
+      <c r="X77" t="n">
+        <v/>
+      </c>
+      <c r="Y77" t="n">
+        <v/>
+      </c>
+      <c r="Z77" t="n">
+        <v/>
+      </c>
+      <c r="AA77" t="n">
+        <v/>
+      </c>
+      <c r="AB77" t="n">
+        <v/>
+      </c>
+      <c r="AC77" t="n">
+        <v/>
+      </c>
+      <c r="AD77" t="n">
+        <v/>
+      </c>
+      <c r="AE77" t="n">
+        <v/>
+      </c>
+      <c r="AF77" t="n">
+        <v/>
+      </c>
+      <c r="AG77" t="n">
+        <v/>
+      </c>
+      <c r="AH77" t="n">
+        <v/>
+      </c>
+      <c r="AI77" t="n">
+        <v/>
+      </c>
+      <c r="AJ77" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -2611,92 +2611,92 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ2" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="3">
@@ -2835,92 +2835,92 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ4" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="5">
@@ -2949,90 +2949,6 @@
         <is>
           <t>EMPTY</t>
         </is>
-      </c>
-      <c r="I5" t="n">
-        <v/>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
-      </c>
-      <c r="R5" t="n">
-        <v/>
-      </c>
-      <c r="S5" t="n">
-        <v/>
-      </c>
-      <c r="T5" t="n">
-        <v/>
-      </c>
-      <c r="U5" t="n">
-        <v/>
-      </c>
-      <c r="V5" t="n">
-        <v/>
-      </c>
-      <c r="W5" t="n">
-        <v/>
-      </c>
-      <c r="X5" t="n">
-        <v/>
-      </c>
-      <c r="Y5" t="n">
-        <v/>
-      </c>
-      <c r="Z5" t="n">
-        <v/>
-      </c>
-      <c r="AA5" t="n">
-        <v/>
-      </c>
-      <c r="AB5" t="n">
-        <v/>
-      </c>
-      <c r="AC5" t="n">
-        <v/>
-      </c>
-      <c r="AD5" t="n">
-        <v/>
-      </c>
-      <c r="AE5" t="n">
-        <v/>
-      </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
-      <c r="AI5" t="n">
-        <v/>
-      </c>
-      <c r="AJ5" t="n">
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -3059,92 +2975,92 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="7">
@@ -3171,7 +3087,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -3283,92 +3199,92 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ8" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="9">
@@ -3398,90 +3314,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v/>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
-      </c>
-      <c r="R9" t="n">
-        <v/>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
-      </c>
-      <c r="AA9" t="n">
-        <v/>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
-        <v/>
-      </c>
-      <c r="AJ9" t="n">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3507,92 +3339,92 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ10" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="11">
@@ -3731,92 +3563,92 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ12" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="13">
@@ -3846,90 +3678,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v/>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
-      <c r="Q13" t="n">
-        <v/>
-      </c>
-      <c r="R13" t="n">
-        <v/>
-      </c>
-      <c r="S13" t="n">
-        <v/>
-      </c>
-      <c r="T13" t="n">
-        <v/>
-      </c>
-      <c r="U13" t="n">
-        <v/>
-      </c>
-      <c r="V13" t="n">
-        <v/>
-      </c>
-      <c r="W13" t="n">
-        <v/>
-      </c>
-      <c r="X13" t="n">
-        <v/>
-      </c>
-      <c r="Y13" t="n">
-        <v/>
-      </c>
-      <c r="Z13" t="n">
-        <v/>
-      </c>
-      <c r="AA13" t="n">
-        <v/>
-      </c>
-      <c r="AB13" t="n">
-        <v/>
-      </c>
-      <c r="AC13" t="n">
-        <v/>
-      </c>
-      <c r="AD13" t="n">
-        <v/>
-      </c>
-      <c r="AE13" t="n">
-        <v/>
-      </c>
-      <c r="AF13" t="n">
-        <v/>
-      </c>
-      <c r="AG13" t="n">
-        <v/>
-      </c>
-      <c r="AH13" t="n">
-        <v/>
-      </c>
-      <c r="AI13" t="n">
-        <v/>
-      </c>
-      <c r="AJ13" t="n">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3955,92 +3703,92 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ14" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="15">
@@ -4070,90 +3818,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v/>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
-      <c r="Q15" t="n">
-        <v/>
-      </c>
-      <c r="R15" t="n">
-        <v/>
-      </c>
-      <c r="S15" t="n">
-        <v/>
-      </c>
-      <c r="T15" t="n">
-        <v/>
-      </c>
-      <c r="U15" t="n">
-        <v/>
-      </c>
-      <c r="V15" t="n">
-        <v/>
-      </c>
-      <c r="W15" t="n">
-        <v/>
-      </c>
-      <c r="X15" t="n">
-        <v/>
-      </c>
-      <c r="Y15" t="n">
-        <v/>
-      </c>
-      <c r="Z15" t="n">
-        <v/>
-      </c>
-      <c r="AA15" t="n">
-        <v/>
-      </c>
-      <c r="AB15" t="n">
-        <v/>
-      </c>
-      <c r="AC15" t="n">
-        <v/>
-      </c>
-      <c r="AD15" t="n">
-        <v/>
-      </c>
-      <c r="AE15" t="n">
-        <v/>
-      </c>
-      <c r="AF15" t="n">
-        <v/>
-      </c>
-      <c r="AG15" t="n">
-        <v/>
-      </c>
-      <c r="AH15" t="n">
-        <v/>
-      </c>
-      <c r="AI15" t="n">
-        <v/>
-      </c>
-      <c r="AJ15" t="n">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4179,92 +3843,92 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="17">
@@ -4294,90 +3958,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v/>
-      </c>
-      <c r="J17" t="n">
-        <v/>
-      </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
-      <c r="Q17" t="n">
-        <v/>
-      </c>
-      <c r="R17" t="n">
-        <v/>
-      </c>
-      <c r="S17" t="n">
-        <v/>
-      </c>
-      <c r="T17" t="n">
-        <v/>
-      </c>
-      <c r="U17" t="n">
-        <v/>
-      </c>
-      <c r="V17" t="n">
-        <v/>
-      </c>
-      <c r="W17" t="n">
-        <v/>
-      </c>
-      <c r="X17" t="n">
-        <v/>
-      </c>
-      <c r="Y17" t="n">
-        <v/>
-      </c>
-      <c r="Z17" t="n">
-        <v/>
-      </c>
-      <c r="AA17" t="n">
-        <v/>
-      </c>
-      <c r="AB17" t="n">
-        <v/>
-      </c>
-      <c r="AC17" t="n">
-        <v/>
-      </c>
-      <c r="AD17" t="n">
-        <v/>
-      </c>
-      <c r="AE17" t="n">
-        <v/>
-      </c>
-      <c r="AF17" t="n">
-        <v/>
-      </c>
-      <c r="AG17" t="n">
-        <v/>
-      </c>
-      <c r="AH17" t="n">
-        <v/>
-      </c>
-      <c r="AI17" t="n">
-        <v/>
-      </c>
-      <c r="AJ17" t="n">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4403,92 +3983,92 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ18" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="19">
@@ -4518,90 +4098,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v/>
-      </c>
-      <c r="J19" t="n">
-        <v/>
-      </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
-      <c r="Q19" t="n">
-        <v/>
-      </c>
-      <c r="R19" t="n">
-        <v/>
-      </c>
-      <c r="S19" t="n">
-        <v/>
-      </c>
-      <c r="T19" t="n">
-        <v/>
-      </c>
-      <c r="U19" t="n">
-        <v/>
-      </c>
-      <c r="V19" t="n">
-        <v/>
-      </c>
-      <c r="W19" t="n">
-        <v/>
-      </c>
-      <c r="X19" t="n">
-        <v/>
-      </c>
-      <c r="Y19" t="n">
-        <v/>
-      </c>
-      <c r="Z19" t="n">
-        <v/>
-      </c>
-      <c r="AA19" t="n">
-        <v/>
-      </c>
-      <c r="AB19" t="n">
-        <v/>
-      </c>
-      <c r="AC19" t="n">
-        <v/>
-      </c>
-      <c r="AD19" t="n">
-        <v/>
-      </c>
-      <c r="AE19" t="n">
-        <v/>
-      </c>
-      <c r="AF19" t="n">
-        <v/>
-      </c>
-      <c r="AG19" t="n">
-        <v/>
-      </c>
-      <c r="AH19" t="n">
-        <v/>
-      </c>
-      <c r="AI19" t="n">
-        <v/>
-      </c>
-      <c r="AJ19" t="n">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4627,92 +4123,92 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ20" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="21">
@@ -4742,90 +4238,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v/>
-      </c>
-      <c r="J21" t="n">
-        <v/>
-      </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
-      <c r="Q21" t="n">
-        <v/>
-      </c>
-      <c r="R21" t="n">
-        <v/>
-      </c>
-      <c r="S21" t="n">
-        <v/>
-      </c>
-      <c r="T21" t="n">
-        <v/>
-      </c>
-      <c r="U21" t="n">
-        <v/>
-      </c>
-      <c r="V21" t="n">
-        <v/>
-      </c>
-      <c r="W21" t="n">
-        <v/>
-      </c>
-      <c r="X21" t="n">
-        <v/>
-      </c>
-      <c r="Y21" t="n">
-        <v/>
-      </c>
-      <c r="Z21" t="n">
-        <v/>
-      </c>
-      <c r="AA21" t="n">
-        <v/>
-      </c>
-      <c r="AB21" t="n">
-        <v/>
-      </c>
-      <c r="AC21" t="n">
-        <v/>
-      </c>
-      <c r="AD21" t="n">
-        <v/>
-      </c>
-      <c r="AE21" t="n">
-        <v/>
-      </c>
-      <c r="AF21" t="n">
-        <v/>
-      </c>
-      <c r="AG21" t="n">
-        <v/>
-      </c>
-      <c r="AH21" t="n">
-        <v/>
-      </c>
-      <c r="AI21" t="n">
-        <v/>
-      </c>
-      <c r="AJ21" t="n">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4851,92 +4263,92 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ22" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="23">
@@ -4966,90 +4378,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v/>
-      </c>
-      <c r="J23" t="n">
-        <v/>
-      </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
-      <c r="L23" t="n">
-        <v/>
-      </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
-      <c r="N23" t="n">
-        <v/>
-      </c>
-      <c r="O23" t="n">
-        <v/>
-      </c>
-      <c r="P23" t="n">
-        <v/>
-      </c>
-      <c r="Q23" t="n">
-        <v/>
-      </c>
-      <c r="R23" t="n">
-        <v/>
-      </c>
-      <c r="S23" t="n">
-        <v/>
-      </c>
-      <c r="T23" t="n">
-        <v/>
-      </c>
-      <c r="U23" t="n">
-        <v/>
-      </c>
-      <c r="V23" t="n">
-        <v/>
-      </c>
-      <c r="W23" t="n">
-        <v/>
-      </c>
-      <c r="X23" t="n">
-        <v/>
-      </c>
-      <c r="Y23" t="n">
-        <v/>
-      </c>
-      <c r="Z23" t="n">
-        <v/>
-      </c>
-      <c r="AA23" t="n">
-        <v/>
-      </c>
-      <c r="AB23" t="n">
-        <v/>
-      </c>
-      <c r="AC23" t="n">
-        <v/>
-      </c>
-      <c r="AD23" t="n">
-        <v/>
-      </c>
-      <c r="AE23" t="n">
-        <v/>
-      </c>
-      <c r="AF23" t="n">
-        <v/>
-      </c>
-      <c r="AG23" t="n">
-        <v/>
-      </c>
-      <c r="AH23" t="n">
-        <v/>
-      </c>
-      <c r="AI23" t="n">
-        <v/>
-      </c>
-      <c r="AJ23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5075,92 +4403,92 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ24" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="25">
@@ -5190,90 +4518,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v/>
-      </c>
-      <c r="J25" t="n">
-        <v/>
-      </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
-      <c r="Q25" t="n">
-        <v/>
-      </c>
-      <c r="R25" t="n">
-        <v/>
-      </c>
-      <c r="S25" t="n">
-        <v/>
-      </c>
-      <c r="T25" t="n">
-        <v/>
-      </c>
-      <c r="U25" t="n">
-        <v/>
-      </c>
-      <c r="V25" t="n">
-        <v/>
-      </c>
-      <c r="W25" t="n">
-        <v/>
-      </c>
-      <c r="X25" t="n">
-        <v/>
-      </c>
-      <c r="Y25" t="n">
-        <v/>
-      </c>
-      <c r="Z25" t="n">
-        <v/>
-      </c>
-      <c r="AA25" t="n">
-        <v/>
-      </c>
-      <c r="AB25" t="n">
-        <v/>
-      </c>
-      <c r="AC25" t="n">
-        <v/>
-      </c>
-      <c r="AD25" t="n">
-        <v/>
-      </c>
-      <c r="AE25" t="n">
-        <v/>
-      </c>
-      <c r="AF25" t="n">
-        <v/>
-      </c>
-      <c r="AG25" t="n">
-        <v/>
-      </c>
-      <c r="AH25" t="n">
-        <v/>
-      </c>
-      <c r="AI25" t="n">
-        <v/>
-      </c>
-      <c r="AJ25" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5299,92 +4543,92 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ26" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="27">
@@ -5414,90 +4658,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v/>
-      </c>
-      <c r="J27" t="n">
-        <v/>
-      </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
-      <c r="Q27" t="n">
-        <v/>
-      </c>
-      <c r="R27" t="n">
-        <v/>
-      </c>
-      <c r="S27" t="n">
-        <v/>
-      </c>
-      <c r="T27" t="n">
-        <v/>
-      </c>
-      <c r="U27" t="n">
-        <v/>
-      </c>
-      <c r="V27" t="n">
-        <v/>
-      </c>
-      <c r="W27" t="n">
-        <v/>
-      </c>
-      <c r="X27" t="n">
-        <v/>
-      </c>
-      <c r="Y27" t="n">
-        <v/>
-      </c>
-      <c r="Z27" t="n">
-        <v/>
-      </c>
-      <c r="AA27" t="n">
-        <v/>
-      </c>
-      <c r="AB27" t="n">
-        <v/>
-      </c>
-      <c r="AC27" t="n">
-        <v/>
-      </c>
-      <c r="AD27" t="n">
-        <v/>
-      </c>
-      <c r="AE27" t="n">
-        <v/>
-      </c>
-      <c r="AF27" t="n">
-        <v/>
-      </c>
-      <c r="AG27" t="n">
-        <v/>
-      </c>
-      <c r="AH27" t="n">
-        <v/>
-      </c>
-      <c r="AI27" t="n">
-        <v/>
-      </c>
-      <c r="AJ27" t="n">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5523,92 +4683,92 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ28" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="29">
@@ -5638,90 +4798,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v/>
-      </c>
-      <c r="J29" t="n">
-        <v/>
-      </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
-      <c r="Q29" t="n">
-        <v/>
-      </c>
-      <c r="R29" t="n">
-        <v/>
-      </c>
-      <c r="S29" t="n">
-        <v/>
-      </c>
-      <c r="T29" t="n">
-        <v/>
-      </c>
-      <c r="U29" t="n">
-        <v/>
-      </c>
-      <c r="V29" t="n">
-        <v/>
-      </c>
-      <c r="W29" t="n">
-        <v/>
-      </c>
-      <c r="X29" t="n">
-        <v/>
-      </c>
-      <c r="Y29" t="n">
-        <v/>
-      </c>
-      <c r="Z29" t="n">
-        <v/>
-      </c>
-      <c r="AA29" t="n">
-        <v/>
-      </c>
-      <c r="AB29" t="n">
-        <v/>
-      </c>
-      <c r="AC29" t="n">
-        <v/>
-      </c>
-      <c r="AD29" t="n">
-        <v/>
-      </c>
-      <c r="AE29" t="n">
-        <v/>
-      </c>
-      <c r="AF29" t="n">
-        <v/>
-      </c>
-      <c r="AG29" t="n">
-        <v/>
-      </c>
-      <c r="AH29" t="n">
-        <v/>
-      </c>
-      <c r="AI29" t="n">
-        <v/>
-      </c>
-      <c r="AJ29" t="n">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5747,92 +4823,92 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ30" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="31">
@@ -5862,90 +4938,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v/>
-      </c>
-      <c r="J31" t="n">
-        <v/>
-      </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
-      <c r="Q31" t="n">
-        <v/>
-      </c>
-      <c r="R31" t="n">
-        <v/>
-      </c>
-      <c r="S31" t="n">
-        <v/>
-      </c>
-      <c r="T31" t="n">
-        <v/>
-      </c>
-      <c r="U31" t="n">
-        <v/>
-      </c>
-      <c r="V31" t="n">
-        <v/>
-      </c>
-      <c r="W31" t="n">
-        <v/>
-      </c>
-      <c r="X31" t="n">
-        <v/>
-      </c>
-      <c r="Y31" t="n">
-        <v/>
-      </c>
-      <c r="Z31" t="n">
-        <v/>
-      </c>
-      <c r="AA31" t="n">
-        <v/>
-      </c>
-      <c r="AB31" t="n">
-        <v/>
-      </c>
-      <c r="AC31" t="n">
-        <v/>
-      </c>
-      <c r="AD31" t="n">
-        <v/>
-      </c>
-      <c r="AE31" t="n">
-        <v/>
-      </c>
-      <c r="AF31" t="n">
-        <v/>
-      </c>
-      <c r="AG31" t="n">
-        <v/>
-      </c>
-      <c r="AH31" t="n">
-        <v/>
-      </c>
-      <c r="AI31" t="n">
-        <v/>
-      </c>
-      <c r="AJ31" t="n">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5971,92 +4963,92 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ32" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="33">
@@ -6086,90 +5078,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v/>
-      </c>
-      <c r="J33" t="n">
-        <v/>
-      </c>
-      <c r="K33" t="n">
-        <v/>
-      </c>
-      <c r="L33" t="n">
-        <v/>
-      </c>
-      <c r="M33" t="n">
-        <v/>
-      </c>
-      <c r="N33" t="n">
-        <v/>
-      </c>
-      <c r="O33" t="n">
-        <v/>
-      </c>
-      <c r="P33" t="n">
-        <v/>
-      </c>
-      <c r="Q33" t="n">
-        <v/>
-      </c>
-      <c r="R33" t="n">
-        <v/>
-      </c>
-      <c r="S33" t="n">
-        <v/>
-      </c>
-      <c r="T33" t="n">
-        <v/>
-      </c>
-      <c r="U33" t="n">
-        <v/>
-      </c>
-      <c r="V33" t="n">
-        <v/>
-      </c>
-      <c r="W33" t="n">
-        <v/>
-      </c>
-      <c r="X33" t="n">
-        <v/>
-      </c>
-      <c r="Y33" t="n">
-        <v/>
-      </c>
-      <c r="Z33" t="n">
-        <v/>
-      </c>
-      <c r="AA33" t="n">
-        <v/>
-      </c>
-      <c r="AB33" t="n">
-        <v/>
-      </c>
-      <c r="AC33" t="n">
-        <v/>
-      </c>
-      <c r="AD33" t="n">
-        <v/>
-      </c>
-      <c r="AE33" t="n">
-        <v/>
-      </c>
-      <c r="AF33" t="n">
-        <v/>
-      </c>
-      <c r="AG33" t="n">
-        <v/>
-      </c>
-      <c r="AH33" t="n">
-        <v/>
-      </c>
-      <c r="AI33" t="n">
-        <v/>
-      </c>
-      <c r="AJ33" t="n">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -6195,92 +5103,92 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ34" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="35">
@@ -6310,90 +5218,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v/>
-      </c>
-      <c r="J35" t="n">
-        <v/>
-      </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v/>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
-      <c r="O35" t="n">
-        <v/>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
-      <c r="Q35" t="n">
-        <v/>
-      </c>
-      <c r="R35" t="n">
-        <v/>
-      </c>
-      <c r="S35" t="n">
-        <v/>
-      </c>
-      <c r="T35" t="n">
-        <v/>
-      </c>
-      <c r="U35" t="n">
-        <v/>
-      </c>
-      <c r="V35" t="n">
-        <v/>
-      </c>
-      <c r="W35" t="n">
-        <v/>
-      </c>
-      <c r="X35" t="n">
-        <v/>
-      </c>
-      <c r="Y35" t="n">
-        <v/>
-      </c>
-      <c r="Z35" t="n">
-        <v/>
-      </c>
-      <c r="AA35" t="n">
-        <v/>
-      </c>
-      <c r="AB35" t="n">
-        <v/>
-      </c>
-      <c r="AC35" t="n">
-        <v/>
-      </c>
-      <c r="AD35" t="n">
-        <v/>
-      </c>
-      <c r="AE35" t="n">
-        <v/>
-      </c>
-      <c r="AF35" t="n">
-        <v/>
-      </c>
-      <c r="AG35" t="n">
-        <v/>
-      </c>
-      <c r="AH35" t="n">
-        <v/>
-      </c>
-      <c r="AI35" t="n">
-        <v/>
-      </c>
-      <c r="AJ35" t="n">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -6419,92 +5243,92 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ36" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="37">
@@ -6534,90 +5358,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v/>
-      </c>
-      <c r="J37" t="n">
-        <v/>
-      </c>
-      <c r="K37" t="n">
-        <v/>
-      </c>
-      <c r="L37" t="n">
-        <v/>
-      </c>
-      <c r="M37" t="n">
-        <v/>
-      </c>
-      <c r="N37" t="n">
-        <v/>
-      </c>
-      <c r="O37" t="n">
-        <v/>
-      </c>
-      <c r="P37" t="n">
-        <v/>
-      </c>
-      <c r="Q37" t="n">
-        <v/>
-      </c>
-      <c r="R37" t="n">
-        <v/>
-      </c>
-      <c r="S37" t="n">
-        <v/>
-      </c>
-      <c r="T37" t="n">
-        <v/>
-      </c>
-      <c r="U37" t="n">
-        <v/>
-      </c>
-      <c r="V37" t="n">
-        <v/>
-      </c>
-      <c r="W37" t="n">
-        <v/>
-      </c>
-      <c r="X37" t="n">
-        <v/>
-      </c>
-      <c r="Y37" t="n">
-        <v/>
-      </c>
-      <c r="Z37" t="n">
-        <v/>
-      </c>
-      <c r="AA37" t="n">
-        <v/>
-      </c>
-      <c r="AB37" t="n">
-        <v/>
-      </c>
-      <c r="AC37" t="n">
-        <v/>
-      </c>
-      <c r="AD37" t="n">
-        <v/>
-      </c>
-      <c r="AE37" t="n">
-        <v/>
-      </c>
-      <c r="AF37" t="n">
-        <v/>
-      </c>
-      <c r="AG37" t="n">
-        <v/>
-      </c>
-      <c r="AH37" t="n">
-        <v/>
-      </c>
-      <c r="AI37" t="n">
-        <v/>
-      </c>
-      <c r="AJ37" t="n">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6643,92 +5383,92 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="J38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="K38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="L38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="M38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="N38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="O38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="P38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Q38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="R38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="S38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="T38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="U38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="V38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="W38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="X38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Y38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AA38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AB38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AC38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AD38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AE38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AF38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AG38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AI38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
       <c r="AJ38" t="n">
-        <v>52694.44444444445</v>
+        <v>20833.33</v>
       </c>
     </row>
     <row r="39">
@@ -6758,90 +5498,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v/>
-      </c>
-      <c r="J39" t="n">
-        <v/>
-      </c>
-      <c r="K39" t="n">
-        <v/>
-      </c>
-      <c r="L39" t="n">
-        <v/>
-      </c>
-      <c r="M39" t="n">
-        <v/>
-      </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
-      <c r="O39" t="n">
-        <v/>
-      </c>
-      <c r="P39" t="n">
-        <v/>
-      </c>
-      <c r="Q39" t="n">
-        <v/>
-      </c>
-      <c r="R39" t="n">
-        <v/>
-      </c>
-      <c r="S39" t="n">
-        <v/>
-      </c>
-      <c r="T39" t="n">
-        <v/>
-      </c>
-      <c r="U39" t="n">
-        <v/>
-      </c>
-      <c r="V39" t="n">
-        <v/>
-      </c>
-      <c r="W39" t="n">
-        <v/>
-      </c>
-      <c r="X39" t="n">
-        <v/>
-      </c>
-      <c r="Y39" t="n">
-        <v/>
-      </c>
-      <c r="Z39" t="n">
-        <v/>
-      </c>
-      <c r="AA39" t="n">
-        <v/>
-      </c>
-      <c r="AB39" t="n">
-        <v/>
-      </c>
-      <c r="AC39" t="n">
-        <v/>
-      </c>
-      <c r="AD39" t="n">
-        <v/>
-      </c>
-      <c r="AE39" t="n">
-        <v/>
-      </c>
-      <c r="AF39" t="n">
-        <v/>
-      </c>
-      <c r="AG39" t="n">
-        <v/>
-      </c>
-      <c r="AH39" t="n">
-        <v/>
-      </c>
-      <c r="AI39" t="n">
-        <v/>
-      </c>
-      <c r="AJ39" t="n">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6867,92 +5523,92 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ40" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="41">
@@ -6982,90 +5638,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v/>
-      </c>
-      <c r="J41" t="n">
-        <v/>
-      </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
-      <c r="Q41" t="n">
-        <v/>
-      </c>
-      <c r="R41" t="n">
-        <v/>
-      </c>
-      <c r="S41" t="n">
-        <v/>
-      </c>
-      <c r="T41" t="n">
-        <v/>
-      </c>
-      <c r="U41" t="n">
-        <v/>
-      </c>
-      <c r="V41" t="n">
-        <v/>
-      </c>
-      <c r="W41" t="n">
-        <v/>
-      </c>
-      <c r="X41" t="n">
-        <v/>
-      </c>
-      <c r="Y41" t="n">
-        <v/>
-      </c>
-      <c r="Z41" t="n">
-        <v/>
-      </c>
-      <c r="AA41" t="n">
-        <v/>
-      </c>
-      <c r="AB41" t="n">
-        <v/>
-      </c>
-      <c r="AC41" t="n">
-        <v/>
-      </c>
-      <c r="AD41" t="n">
-        <v/>
-      </c>
-      <c r="AE41" t="n">
-        <v/>
-      </c>
-      <c r="AF41" t="n">
-        <v/>
-      </c>
-      <c r="AG41" t="n">
-        <v/>
-      </c>
-      <c r="AH41" t="n">
-        <v/>
-      </c>
-      <c r="AI41" t="n">
-        <v/>
-      </c>
-      <c r="AJ41" t="n">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -7091,92 +5663,92 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ42" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="43">
@@ -7315,92 +5887,92 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="J44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="K44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="L44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="M44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="N44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="O44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="P44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="Q44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="R44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="S44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="T44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="U44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="V44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="W44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="X44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="Y44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="Z44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="AA44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="AB44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="AC44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="AD44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="AE44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="AF44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="AG44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="AH44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="AI44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ44" t="n">
-        <v>42050.82742316784</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="45">
@@ -7427,7 +5999,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -7539,92 +6111,92 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ46" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="47">
@@ -7654,90 +6226,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v/>
-      </c>
-      <c r="J47" t="n">
-        <v/>
-      </c>
-      <c r="K47" t="n">
-        <v/>
-      </c>
-      <c r="L47" t="n">
-        <v/>
-      </c>
-      <c r="M47" t="n">
-        <v/>
-      </c>
-      <c r="N47" t="n">
-        <v/>
-      </c>
-      <c r="O47" t="n">
-        <v/>
-      </c>
-      <c r="P47" t="n">
-        <v/>
-      </c>
-      <c r="Q47" t="n">
-        <v/>
-      </c>
-      <c r="R47" t="n">
-        <v/>
-      </c>
-      <c r="S47" t="n">
-        <v/>
-      </c>
-      <c r="T47" t="n">
-        <v/>
-      </c>
-      <c r="U47" t="n">
-        <v/>
-      </c>
-      <c r="V47" t="n">
-        <v/>
-      </c>
-      <c r="W47" t="n">
-        <v/>
-      </c>
-      <c r="X47" t="n">
-        <v/>
-      </c>
-      <c r="Y47" t="n">
-        <v/>
-      </c>
-      <c r="Z47" t="n">
-        <v/>
-      </c>
-      <c r="AA47" t="n">
-        <v/>
-      </c>
-      <c r="AB47" t="n">
-        <v/>
-      </c>
-      <c r="AC47" t="n">
-        <v/>
-      </c>
-      <c r="AD47" t="n">
-        <v/>
-      </c>
-      <c r="AE47" t="n">
-        <v/>
-      </c>
-      <c r="AF47" t="n">
-        <v/>
-      </c>
-      <c r="AG47" t="n">
-        <v/>
-      </c>
-      <c r="AH47" t="n">
-        <v/>
-      </c>
-      <c r="AI47" t="n">
-        <v/>
-      </c>
-      <c r="AJ47" t="n">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7763,92 +6251,92 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ48" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="49">
@@ -7987,92 +6475,92 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ50" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="51">
@@ -8102,90 +6590,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v/>
-      </c>
-      <c r="J51" t="n">
-        <v/>
-      </c>
-      <c r="K51" t="n">
-        <v/>
-      </c>
-      <c r="L51" t="n">
-        <v/>
-      </c>
-      <c r="M51" t="n">
-        <v/>
-      </c>
-      <c r="N51" t="n">
-        <v/>
-      </c>
-      <c r="O51" t="n">
-        <v/>
-      </c>
-      <c r="P51" t="n">
-        <v/>
-      </c>
-      <c r="Q51" t="n">
-        <v/>
-      </c>
-      <c r="R51" t="n">
-        <v/>
-      </c>
-      <c r="S51" t="n">
-        <v/>
-      </c>
-      <c r="T51" t="n">
-        <v/>
-      </c>
-      <c r="U51" t="n">
-        <v/>
-      </c>
-      <c r="V51" t="n">
-        <v/>
-      </c>
-      <c r="W51" t="n">
-        <v/>
-      </c>
-      <c r="X51" t="n">
-        <v/>
-      </c>
-      <c r="Y51" t="n">
-        <v/>
-      </c>
-      <c r="Z51" t="n">
-        <v/>
-      </c>
-      <c r="AA51" t="n">
-        <v/>
-      </c>
-      <c r="AB51" t="n">
-        <v/>
-      </c>
-      <c r="AC51" t="n">
-        <v/>
-      </c>
-      <c r="AD51" t="n">
-        <v/>
-      </c>
-      <c r="AE51" t="n">
-        <v/>
-      </c>
-      <c r="AF51" t="n">
-        <v/>
-      </c>
-      <c r="AG51" t="n">
-        <v/>
-      </c>
-      <c r="AH51" t="n">
-        <v/>
-      </c>
-      <c r="AI51" t="n">
-        <v/>
-      </c>
-      <c r="AJ51" t="n">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8211,92 +6615,92 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ52" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="53">
@@ -8326,90 +6730,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v/>
-      </c>
-      <c r="J53" t="n">
-        <v/>
-      </c>
-      <c r="K53" t="n">
-        <v/>
-      </c>
-      <c r="L53" t="n">
-        <v/>
-      </c>
-      <c r="M53" t="n">
-        <v/>
-      </c>
-      <c r="N53" t="n">
-        <v/>
-      </c>
-      <c r="O53" t="n">
-        <v/>
-      </c>
-      <c r="P53" t="n">
-        <v/>
-      </c>
-      <c r="Q53" t="n">
-        <v/>
-      </c>
-      <c r="R53" t="n">
-        <v/>
-      </c>
-      <c r="S53" t="n">
-        <v/>
-      </c>
-      <c r="T53" t="n">
-        <v/>
-      </c>
-      <c r="U53" t="n">
-        <v/>
-      </c>
-      <c r="V53" t="n">
-        <v/>
-      </c>
-      <c r="W53" t="n">
-        <v/>
-      </c>
-      <c r="X53" t="n">
-        <v/>
-      </c>
-      <c r="Y53" t="n">
-        <v/>
-      </c>
-      <c r="Z53" t="n">
-        <v/>
-      </c>
-      <c r="AA53" t="n">
-        <v/>
-      </c>
-      <c r="AB53" t="n">
-        <v/>
-      </c>
-      <c r="AC53" t="n">
-        <v/>
-      </c>
-      <c r="AD53" t="n">
-        <v/>
-      </c>
-      <c r="AE53" t="n">
-        <v/>
-      </c>
-      <c r="AF53" t="n">
-        <v/>
-      </c>
-      <c r="AG53" t="n">
-        <v/>
-      </c>
-      <c r="AH53" t="n">
-        <v/>
-      </c>
-      <c r="AI53" t="n">
-        <v/>
-      </c>
-      <c r="AJ53" t="n">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8435,92 +6755,92 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ54" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="55">
@@ -8550,90 +6870,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v/>
-      </c>
-      <c r="J55" t="n">
-        <v/>
-      </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
-      <c r="Q55" t="n">
-        <v/>
-      </c>
-      <c r="R55" t="n">
-        <v/>
-      </c>
-      <c r="S55" t="n">
-        <v/>
-      </c>
-      <c r="T55" t="n">
-        <v/>
-      </c>
-      <c r="U55" t="n">
-        <v/>
-      </c>
-      <c r="V55" t="n">
-        <v/>
-      </c>
-      <c r="W55" t="n">
-        <v/>
-      </c>
-      <c r="X55" t="n">
-        <v/>
-      </c>
-      <c r="Y55" t="n">
-        <v/>
-      </c>
-      <c r="Z55" t="n">
-        <v/>
-      </c>
-      <c r="AA55" t="n">
-        <v/>
-      </c>
-      <c r="AB55" t="n">
-        <v/>
-      </c>
-      <c r="AC55" t="n">
-        <v/>
-      </c>
-      <c r="AD55" t="n">
-        <v/>
-      </c>
-      <c r="AE55" t="n">
-        <v/>
-      </c>
-      <c r="AF55" t="n">
-        <v/>
-      </c>
-      <c r="AG55" t="n">
-        <v/>
-      </c>
-      <c r="AH55" t="n">
-        <v/>
-      </c>
-      <c r="AI55" t="n">
-        <v/>
-      </c>
-      <c r="AJ55" t="n">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8659,92 +6895,92 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ56" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="57">
@@ -8774,90 +7010,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v/>
-      </c>
-      <c r="J57" t="n">
-        <v/>
-      </c>
-      <c r="K57" t="n">
-        <v/>
-      </c>
-      <c r="L57" t="n">
-        <v/>
-      </c>
-      <c r="M57" t="n">
-        <v/>
-      </c>
-      <c r="N57" t="n">
-        <v/>
-      </c>
-      <c r="O57" t="n">
-        <v/>
-      </c>
-      <c r="P57" t="n">
-        <v/>
-      </c>
-      <c r="Q57" t="n">
-        <v/>
-      </c>
-      <c r="R57" t="n">
-        <v/>
-      </c>
-      <c r="S57" t="n">
-        <v/>
-      </c>
-      <c r="T57" t="n">
-        <v/>
-      </c>
-      <c r="U57" t="n">
-        <v/>
-      </c>
-      <c r="V57" t="n">
-        <v/>
-      </c>
-      <c r="W57" t="n">
-        <v/>
-      </c>
-      <c r="X57" t="n">
-        <v/>
-      </c>
-      <c r="Y57" t="n">
-        <v/>
-      </c>
-      <c r="Z57" t="n">
-        <v/>
-      </c>
-      <c r="AA57" t="n">
-        <v/>
-      </c>
-      <c r="AB57" t="n">
-        <v/>
-      </c>
-      <c r="AC57" t="n">
-        <v/>
-      </c>
-      <c r="AD57" t="n">
-        <v/>
-      </c>
-      <c r="AE57" t="n">
-        <v/>
-      </c>
-      <c r="AF57" t="n">
-        <v/>
-      </c>
-      <c r="AG57" t="n">
-        <v/>
-      </c>
-      <c r="AH57" t="n">
-        <v/>
-      </c>
-      <c r="AI57" t="n">
-        <v/>
-      </c>
-      <c r="AJ57" t="n">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8883,92 +7035,92 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ58" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="59">
@@ -8998,90 +7150,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v/>
-      </c>
-      <c r="J59" t="n">
-        <v/>
-      </c>
-      <c r="K59" t="n">
-        <v/>
-      </c>
-      <c r="L59" t="n">
-        <v/>
-      </c>
-      <c r="M59" t="n">
-        <v/>
-      </c>
-      <c r="N59" t="n">
-        <v/>
-      </c>
-      <c r="O59" t="n">
-        <v/>
-      </c>
-      <c r="P59" t="n">
-        <v/>
-      </c>
-      <c r="Q59" t="n">
-        <v/>
-      </c>
-      <c r="R59" t="n">
-        <v/>
-      </c>
-      <c r="S59" t="n">
-        <v/>
-      </c>
-      <c r="T59" t="n">
-        <v/>
-      </c>
-      <c r="U59" t="n">
-        <v/>
-      </c>
-      <c r="V59" t="n">
-        <v/>
-      </c>
-      <c r="W59" t="n">
-        <v/>
-      </c>
-      <c r="X59" t="n">
-        <v/>
-      </c>
-      <c r="Y59" t="n">
-        <v/>
-      </c>
-      <c r="Z59" t="n">
-        <v/>
-      </c>
-      <c r="AA59" t="n">
-        <v/>
-      </c>
-      <c r="AB59" t="n">
-        <v/>
-      </c>
-      <c r="AC59" t="n">
-        <v/>
-      </c>
-      <c r="AD59" t="n">
-        <v/>
-      </c>
-      <c r="AE59" t="n">
-        <v/>
-      </c>
-      <c r="AF59" t="n">
-        <v/>
-      </c>
-      <c r="AG59" t="n">
-        <v/>
-      </c>
-      <c r="AH59" t="n">
-        <v/>
-      </c>
-      <c r="AI59" t="n">
-        <v/>
-      </c>
-      <c r="AJ59" t="n">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9107,92 +7175,92 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ60" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="61">
@@ -9222,90 +7290,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v/>
-      </c>
-      <c r="J61" t="n">
-        <v/>
-      </c>
-      <c r="K61" t="n">
-        <v/>
-      </c>
-      <c r="L61" t="n">
-        <v/>
-      </c>
-      <c r="M61" t="n">
-        <v/>
-      </c>
-      <c r="N61" t="n">
-        <v/>
-      </c>
-      <c r="O61" t="n">
-        <v/>
-      </c>
-      <c r="P61" t="n">
-        <v/>
-      </c>
-      <c r="Q61" t="n">
-        <v/>
-      </c>
-      <c r="R61" t="n">
-        <v/>
-      </c>
-      <c r="S61" t="n">
-        <v/>
-      </c>
-      <c r="T61" t="n">
-        <v/>
-      </c>
-      <c r="U61" t="n">
-        <v/>
-      </c>
-      <c r="V61" t="n">
-        <v/>
-      </c>
-      <c r="W61" t="n">
-        <v/>
-      </c>
-      <c r="X61" t="n">
-        <v/>
-      </c>
-      <c r="Y61" t="n">
-        <v/>
-      </c>
-      <c r="Z61" t="n">
-        <v/>
-      </c>
-      <c r="AA61" t="n">
-        <v/>
-      </c>
-      <c r="AB61" t="n">
-        <v/>
-      </c>
-      <c r="AC61" t="n">
-        <v/>
-      </c>
-      <c r="AD61" t="n">
-        <v/>
-      </c>
-      <c r="AE61" t="n">
-        <v/>
-      </c>
-      <c r="AF61" t="n">
-        <v/>
-      </c>
-      <c r="AG61" t="n">
-        <v/>
-      </c>
-      <c r="AH61" t="n">
-        <v/>
-      </c>
-      <c r="AI61" t="n">
-        <v/>
-      </c>
-      <c r="AJ61" t="n">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9331,92 +7315,92 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ62" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="63">
@@ -9555,92 +7539,92 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ64" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="65">
@@ -9779,92 +7763,92 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ66" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="67">
@@ -9894,90 +7878,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v/>
-      </c>
-      <c r="J67" t="n">
-        <v/>
-      </c>
-      <c r="K67" t="n">
-        <v/>
-      </c>
-      <c r="L67" t="n">
-        <v/>
-      </c>
-      <c r="M67" t="n">
-        <v/>
-      </c>
-      <c r="N67" t="n">
-        <v/>
-      </c>
-      <c r="O67" t="n">
-        <v/>
-      </c>
-      <c r="P67" t="n">
-        <v/>
-      </c>
-      <c r="Q67" t="n">
-        <v/>
-      </c>
-      <c r="R67" t="n">
-        <v/>
-      </c>
-      <c r="S67" t="n">
-        <v/>
-      </c>
-      <c r="T67" t="n">
-        <v/>
-      </c>
-      <c r="U67" t="n">
-        <v/>
-      </c>
-      <c r="V67" t="n">
-        <v/>
-      </c>
-      <c r="W67" t="n">
-        <v/>
-      </c>
-      <c r="X67" t="n">
-        <v/>
-      </c>
-      <c r="Y67" t="n">
-        <v/>
-      </c>
-      <c r="Z67" t="n">
-        <v/>
-      </c>
-      <c r="AA67" t="n">
-        <v/>
-      </c>
-      <c r="AB67" t="n">
-        <v/>
-      </c>
-      <c r="AC67" t="n">
-        <v/>
-      </c>
-      <c r="AD67" t="n">
-        <v/>
-      </c>
-      <c r="AE67" t="n">
-        <v/>
-      </c>
-      <c r="AF67" t="n">
-        <v/>
-      </c>
-      <c r="AG67" t="n">
-        <v/>
-      </c>
-      <c r="AH67" t="n">
-        <v/>
-      </c>
-      <c r="AI67" t="n">
-        <v/>
-      </c>
-      <c r="AJ67" t="n">
-        <v/>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -10003,92 +7903,92 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ68" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="69">
@@ -10118,90 +8018,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v/>
-      </c>
-      <c r="J69" t="n">
-        <v/>
-      </c>
-      <c r="K69" t="n">
-        <v/>
-      </c>
-      <c r="L69" t="n">
-        <v/>
-      </c>
-      <c r="M69" t="n">
-        <v/>
-      </c>
-      <c r="N69" t="n">
-        <v/>
-      </c>
-      <c r="O69" t="n">
-        <v/>
-      </c>
-      <c r="P69" t="n">
-        <v/>
-      </c>
-      <c r="Q69" t="n">
-        <v/>
-      </c>
-      <c r="R69" t="n">
-        <v/>
-      </c>
-      <c r="S69" t="n">
-        <v/>
-      </c>
-      <c r="T69" t="n">
-        <v/>
-      </c>
-      <c r="U69" t="n">
-        <v/>
-      </c>
-      <c r="V69" t="n">
-        <v/>
-      </c>
-      <c r="W69" t="n">
-        <v/>
-      </c>
-      <c r="X69" t="n">
-        <v/>
-      </c>
-      <c r="Y69" t="n">
-        <v/>
-      </c>
-      <c r="Z69" t="n">
-        <v/>
-      </c>
-      <c r="AA69" t="n">
-        <v/>
-      </c>
-      <c r="AB69" t="n">
-        <v/>
-      </c>
-      <c r="AC69" t="n">
-        <v/>
-      </c>
-      <c r="AD69" t="n">
-        <v/>
-      </c>
-      <c r="AE69" t="n">
-        <v/>
-      </c>
-      <c r="AF69" t="n">
-        <v/>
-      </c>
-      <c r="AG69" t="n">
-        <v/>
-      </c>
-      <c r="AH69" t="n">
-        <v/>
-      </c>
-      <c r="AI69" t="n">
-        <v/>
-      </c>
-      <c r="AJ69" t="n">
-        <v/>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -10227,92 +8043,92 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ70" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="71">
@@ -10342,90 +8158,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v/>
-      </c>
-      <c r="J71" t="n">
-        <v/>
-      </c>
-      <c r="K71" t="n">
-        <v/>
-      </c>
-      <c r="L71" t="n">
-        <v/>
-      </c>
-      <c r="M71" t="n">
-        <v/>
-      </c>
-      <c r="N71" t="n">
-        <v/>
-      </c>
-      <c r="O71" t="n">
-        <v/>
-      </c>
-      <c r="P71" t="n">
-        <v/>
-      </c>
-      <c r="Q71" t="n">
-        <v/>
-      </c>
-      <c r="R71" t="n">
-        <v/>
-      </c>
-      <c r="S71" t="n">
-        <v/>
-      </c>
-      <c r="T71" t="n">
-        <v/>
-      </c>
-      <c r="U71" t="n">
-        <v/>
-      </c>
-      <c r="V71" t="n">
-        <v/>
-      </c>
-      <c r="W71" t="n">
-        <v/>
-      </c>
-      <c r="X71" t="n">
-        <v/>
-      </c>
-      <c r="Y71" t="n">
-        <v/>
-      </c>
-      <c r="Z71" t="n">
-        <v/>
-      </c>
-      <c r="AA71" t="n">
-        <v/>
-      </c>
-      <c r="AB71" t="n">
-        <v/>
-      </c>
-      <c r="AC71" t="n">
-        <v/>
-      </c>
-      <c r="AD71" t="n">
-        <v/>
-      </c>
-      <c r="AE71" t="n">
-        <v/>
-      </c>
-      <c r="AF71" t="n">
-        <v/>
-      </c>
-      <c r="AG71" t="n">
-        <v/>
-      </c>
-      <c r="AH71" t="n">
-        <v/>
-      </c>
-      <c r="AI71" t="n">
-        <v/>
-      </c>
-      <c r="AJ71" t="n">
-        <v/>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10451,92 +8183,92 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ72" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="73">
@@ -10566,90 +8298,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v/>
-      </c>
-      <c r="J73" t="n">
-        <v/>
-      </c>
-      <c r="K73" t="n">
-        <v/>
-      </c>
-      <c r="L73" t="n">
-        <v/>
-      </c>
-      <c r="M73" t="n">
-        <v/>
-      </c>
-      <c r="N73" t="n">
-        <v/>
-      </c>
-      <c r="O73" t="n">
-        <v/>
-      </c>
-      <c r="P73" t="n">
-        <v/>
-      </c>
-      <c r="Q73" t="n">
-        <v/>
-      </c>
-      <c r="R73" t="n">
-        <v/>
-      </c>
-      <c r="S73" t="n">
-        <v/>
-      </c>
-      <c r="T73" t="n">
-        <v/>
-      </c>
-      <c r="U73" t="n">
-        <v/>
-      </c>
-      <c r="V73" t="n">
-        <v/>
-      </c>
-      <c r="W73" t="n">
-        <v/>
-      </c>
-      <c r="X73" t="n">
-        <v/>
-      </c>
-      <c r="Y73" t="n">
-        <v/>
-      </c>
-      <c r="Z73" t="n">
-        <v/>
-      </c>
-      <c r="AA73" t="n">
-        <v/>
-      </c>
-      <c r="AB73" t="n">
-        <v/>
-      </c>
-      <c r="AC73" t="n">
-        <v/>
-      </c>
-      <c r="AD73" t="n">
-        <v/>
-      </c>
-      <c r="AE73" t="n">
-        <v/>
-      </c>
-      <c r="AF73" t="n">
-        <v/>
-      </c>
-      <c r="AG73" t="n">
-        <v/>
-      </c>
-      <c r="AH73" t="n">
-        <v/>
-      </c>
-      <c r="AI73" t="n">
-        <v/>
-      </c>
-      <c r="AJ73" t="n">
-        <v/>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10675,92 +8323,92 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ74" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="75">
@@ -10790,90 +8438,6 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v/>
-      </c>
-      <c r="J75" t="n">
-        <v/>
-      </c>
-      <c r="K75" t="n">
-        <v/>
-      </c>
-      <c r="L75" t="n">
-        <v/>
-      </c>
-      <c r="M75" t="n">
-        <v/>
-      </c>
-      <c r="N75" t="n">
-        <v/>
-      </c>
-      <c r="O75" t="n">
-        <v/>
-      </c>
-      <c r="P75" t="n">
-        <v/>
-      </c>
-      <c r="Q75" t="n">
-        <v/>
-      </c>
-      <c r="R75" t="n">
-        <v/>
-      </c>
-      <c r="S75" t="n">
-        <v/>
-      </c>
-      <c r="T75" t="n">
-        <v/>
-      </c>
-      <c r="U75" t="n">
-        <v/>
-      </c>
-      <c r="V75" t="n">
-        <v/>
-      </c>
-      <c r="W75" t="n">
-        <v/>
-      </c>
-      <c r="X75" t="n">
-        <v/>
-      </c>
-      <c r="Y75" t="n">
-        <v/>
-      </c>
-      <c r="Z75" t="n">
-        <v/>
-      </c>
-      <c r="AA75" t="n">
-        <v/>
-      </c>
-      <c r="AB75" t="n">
-        <v/>
-      </c>
-      <c r="AC75" t="n">
-        <v/>
-      </c>
-      <c r="AD75" t="n">
-        <v/>
-      </c>
-      <c r="AE75" t="n">
-        <v/>
-      </c>
-      <c r="AF75" t="n">
-        <v/>
-      </c>
-      <c r="AG75" t="n">
-        <v/>
-      </c>
-      <c r="AH75" t="n">
-        <v/>
-      </c>
-      <c r="AI75" t="n">
-        <v/>
-      </c>
-      <c r="AJ75" t="n">
-        <v/>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10899,92 +8463,92 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="J76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="K76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="L76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="M76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="N76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="O76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="P76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Q76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="R76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="S76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="T76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="U76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="V76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="W76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="X76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Y76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="Z76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AA76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AB76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AC76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AD76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AE76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AF76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AG76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AH76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AI76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
       <c r="AJ76" t="n">
-        <v>42050.82742316785</v>
+        <v>32777.77</v>
       </c>
     </row>
     <row r="77">
@@ -11013,90 +8577,6 @@
         <is>
           <t>EMPTY</t>
         </is>
-      </c>
-      <c r="I77" t="n">
-        <v/>
-      </c>
-      <c r="J77" t="n">
-        <v/>
-      </c>
-      <c r="K77" t="n">
-        <v/>
-      </c>
-      <c r="L77" t="n">
-        <v/>
-      </c>
-      <c r="M77" t="n">
-        <v/>
-      </c>
-      <c r="N77" t="n">
-        <v/>
-      </c>
-      <c r="O77" t="n">
-        <v/>
-      </c>
-      <c r="P77" t="n">
-        <v/>
-      </c>
-      <c r="Q77" t="n">
-        <v/>
-      </c>
-      <c r="R77" t="n">
-        <v/>
-      </c>
-      <c r="S77" t="n">
-        <v/>
-      </c>
-      <c r="T77" t="n">
-        <v/>
-      </c>
-      <c r="U77" t="n">
-        <v/>
-      </c>
-      <c r="V77" t="n">
-        <v/>
-      </c>
-      <c r="W77" t="n">
-        <v/>
-      </c>
-      <c r="X77" t="n">
-        <v/>
-      </c>
-      <c r="Y77" t="n">
-        <v/>
-      </c>
-      <c r="Z77" t="n">
-        <v/>
-      </c>
-      <c r="AA77" t="n">
-        <v/>
-      </c>
-      <c r="AB77" t="n">
-        <v/>
-      </c>
-      <c r="AC77" t="n">
-        <v/>
-      </c>
-      <c r="AD77" t="n">
-        <v/>
-      </c>
-      <c r="AE77" t="n">
-        <v/>
-      </c>
-      <c r="AF77" t="n">
-        <v/>
-      </c>
-      <c r="AG77" t="n">
-        <v/>
-      </c>
-      <c r="AH77" t="n">
-        <v/>
-      </c>
-      <c r="AI77" t="n">
-        <v/>
-      </c>
-      <c r="AJ77" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
